--- a/data/Needs Assessment Criteria_Scores.xlsx
+++ b/data/Needs Assessment Criteria_Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hntb.sharepoint.com/sites/dp_67985_BMPI_WA02/Shared Documents/WA02/2.0_Feas_Stdy/D. Existing Conditions and Needs Assessment/Needs Assessment/r2r_tool/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1182" documentId="8_{7946392A-2ACF-41B0-B056-8AE476578779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EB6EFA7-FCBD-4449-B698-1D3F0511FCA8}"/>
+  <xr:revisionPtr revIDLastSave="1404" documentId="8_{7946392A-2ACF-41B0-B056-8AE476578779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{515DA79A-A557-4D04-A7E0-9D7D9801CC01}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{E1CAF611-0EF8-45C8-ADE8-F67A889F5FFF}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{E1CAF611-0EF8-45C8-ADE8-F67A889F5FFF}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$2:$AT$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'data with previous weighted avg'!$A$2:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data_CLEAN!$A$2:$Y$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">data_MAPPING!$A$1:$K$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">data_SCORING!$A$2:$Y$58</definedName>
     <definedName name="_xlnm.Database">MultimodalConnectivity_Corridor!$A$1:$K$57</definedName>
   </definedNames>
@@ -113,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="340">
   <si>
     <t>mobility, reliability, and connectvity</t>
   </si>
@@ -984,16 +985,191 @@
   <si>
     <t>Access to Rest Areas/Truck Parking</t>
   </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>US 83 (Kimble to Dimmit County)</t>
+  </si>
+  <si>
+    <t>SH 173 (Kerr to  Frio County)</t>
+  </si>
+  <si>
+    <t>US 90 (Medina to Val Verde County)</t>
+  </si>
+  <si>
+    <t>US 83 (Starr to Webb County)</t>
+  </si>
+  <si>
+    <t>US 90 (Terrell to Culberson County)</t>
+  </si>
+  <si>
+    <t>SH 44 (Jim Wells to Duval County)</t>
+  </si>
+  <si>
+    <t>Corridor_excel</t>
+  </si>
+  <si>
+    <t>Mark_Access_score</t>
+  </si>
+  <si>
+    <t>Pe_G_M_score</t>
+  </si>
+  <si>
+    <t>Net_Desg_score</t>
+  </si>
+  <si>
+    <t>Percentiles for Network Designation Scores</t>
+  </si>
+  <si>
+    <t>People and Goods Movement</t>
+  </si>
+  <si>
+    <t>Market Access</t>
+  </si>
+  <si>
+    <t>Network Designation Score</t>
+  </si>
+  <si>
+    <t>Percentiles for Needs Assessment Score</t>
+  </si>
+  <si>
+    <t>Needs_Cat</t>
+  </si>
+  <si>
+    <t>ND_Cat</t>
+  </si>
+  <si>
+    <t>Mobility, Reliability, &amp; Connectivity</t>
+  </si>
+  <si>
+    <t>Safety &amp; Security</t>
+  </si>
+  <si>
+    <t>Needs Assessment</t>
+  </si>
+  <si>
+    <t>Network Designation</t>
+  </si>
+  <si>
+    <t>Corridor Needs</t>
+  </si>
+  <si>
+    <t>Corridor Importance</t>
+  </si>
+  <si>
+    <t>No Data</t>
+  </si>
+  <si>
+    <r>
+      <t>Asset Preservation and Technology Deployment</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Customer Service, Stewardship and Sustainability, and Equity</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>SH 17</t>
+  </si>
+  <si>
+    <t>SH 20</t>
+  </si>
+  <si>
+    <t>US 67</t>
+  </si>
+  <si>
+    <t>SH 85</t>
+  </si>
+  <si>
+    <t>SH 97</t>
+  </si>
+  <si>
+    <t>SH 72</t>
+  </si>
+  <si>
+    <t>US 59</t>
+  </si>
+  <si>
+    <t>SL 79</t>
+  </si>
+  <si>
+    <t>SL 195</t>
+  </si>
+  <si>
+    <t>SH 44 (Webb to Duval County)</t>
+  </si>
+  <si>
+    <t>US 67/90 (Presidio to Brewster County)</t>
+  </si>
+  <si>
+    <t>SH 359 (Webb to Jim Hogg County)</t>
+  </si>
+  <si>
+    <t>SH 359 (Jim Hogg to Duval County)</t>
+  </si>
+  <si>
+    <t>SH 359 (Jim Wells County)</t>
+  </si>
+  <si>
+    <t>SH 173 (Atascosa County)</t>
+  </si>
+  <si>
+    <t>SH 16 (Atascosa to Zapata County)</t>
+  </si>
+  <si>
+    <t>SH 16 (Bandera County)</t>
+  </si>
+  <si>
+    <t>US 277 (Schleicher to Val Verde County)</t>
+  </si>
+  <si>
+    <t>US 277 (Val Verde to Dimmit County)</t>
+  </si>
+  <si>
+    <t>US 83 (Webb County)</t>
+  </si>
+  <si>
+    <t>SL 480 (N Eagle Pass)</t>
+  </si>
+  <si>
+    <t>SL 480 (S Eagle Pass)</t>
+  </si>
+  <si>
+    <t>240AA1005 (Webb County)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000000000"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1017,8 +1193,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Verdana"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1055,8 +1249,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0056A9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBD1E2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E9F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1425,32 +1643,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1466,10 +1658,123 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
+        <color rgb="FF0056A9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF0056A9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF0056A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF0056A9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF0056A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF0056A9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF0056A9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF0056A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF0056A9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF0056A9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF0056A9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF0056A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -1481,7 +1786,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -1490,16 +1795,25 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="double">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -1648,29 +1962,110 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1694,8 +2089,64 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor auto="1"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5A33"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF5A33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -10255,60 +10706,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="C1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81" t="s">
+      <c r="C1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81" t="s">
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
+      <c r="AJ1" s="108"/>
+      <c r="AK1" s="108"/>
+      <c r="AL1" s="108"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
       <c r="AP1" t="s">
         <v>92</v>
       </c>
-      <c r="AQ1" s="81" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
+      <c r="AQ1" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR1" s="108"/>
+      <c r="AS1" s="108"/>
+      <c r="AT1" s="108"/>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -18894,37 +19345,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81" t="s">
+      <c r="C1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -23526,37 +23977,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="C1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81" t="s">
+      <c r="C1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -30384,7 +30835,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D177C5-493A-4F32-ACB5-4E188C9C693E}">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
@@ -30394,9 +30845,12 @@
     <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -30421,1466 +30875,2604 @@
       <c r="H1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J1" t="s">
+        <v>299</v>
+      </c>
+      <c r="K1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L1" t="s">
+        <v>306</v>
+      </c>
+      <c r="M1" t="s">
+        <v>307</v>
+      </c>
+      <c r="N1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="68">
-        <v>190.605222900999</v>
+        <v>64</v>
+      </c>
+      <c r="B2">
+        <v>95.0268986208999</v>
       </c>
       <c r="C2">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>1.4285714285714284</v>
       </c>
       <c r="F2">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="G2">
-        <v>2.3125</v>
+        <v>1.3196428571428571</v>
       </c>
       <c r="H2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="I2">
+        <v>3.1472760283264498</v>
+      </c>
+      <c r="J2">
+        <v>2.4124289188575898</v>
+      </c>
+      <c r="K2">
+        <v>5.6481793579727704</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G2&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M2" t="str">
+        <f>IF(K2&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K2&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B3">
-        <v>84.428982097299894</v>
+        <v>26.949391069800001</v>
       </c>
       <c r="C3">
-        <v>2.3000000000000003</v>
+        <v>1.8</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F3">
+        <v>1.25</v>
+      </c>
+      <c r="G3">
+        <v>1.4410714285714286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3">
+        <v>3.7234378344332399</v>
+      </c>
+      <c r="J3">
+        <v>2.6507947947551598</v>
+      </c>
+      <c r="K3">
+        <v>6.2952041319554404</v>
+      </c>
+      <c r="L3" t="str">
+        <f>IF(G3&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G3&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M3" t="str">
+        <f>IF(K3&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K3&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="2">
+        <v>42.901241016900002</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="2">
         <v>1.4285714285714284</v>
       </c>
-      <c r="F3">
-        <v>2.5</v>
-      </c>
-      <c r="G3">
-        <v>2.3071428571428574</v>
-      </c>
-      <c r="H3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4">
-        <v>206.581413717</v>
-      </c>
-      <c r="C4">
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2.75</v>
-      </c>
-      <c r="G4">
-        <v>2.2625000000000002</v>
-      </c>
-      <c r="H4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1.6821428571428569</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3.4583333333333299</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2.7111111111111099</v>
+      </c>
+      <c r="K4" s="2">
+        <v>6.06944444444445</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <f>IF(G4&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G4&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <f>IF(K4&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K4&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B5">
-        <v>108.143126791</v>
+        <v>42.291837041199898</v>
       </c>
       <c r="C5">
-        <v>2.8000000000000003</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D5">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>1.1428571428571428</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="F5">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2.2357142857142858</v>
+        <v>1.5285714285714287</v>
       </c>
       <c r="H5" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="I5">
+        <v>2.8444312929403499</v>
+      </c>
+      <c r="J5">
+        <v>2.7461905105387898</v>
+      </c>
+      <c r="K5">
+        <v>5.6088888742303498</v>
+      </c>
+      <c r="L5" t="str">
+        <f>IF(G5&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G5&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M5" t="str">
+        <f>IF(K5&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K5&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B6">
-        <v>97.960131788799899</v>
+        <v>3.4067871411100001</v>
       </c>
       <c r="C6">
-        <v>2.3000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="D6">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>1.2857142857142856</v>
+        <v>1.4285714285714284</v>
       </c>
       <c r="F6">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="G6">
-        <v>2.2089285714285714</v>
+        <v>1.5696428571428571</v>
       </c>
       <c r="H6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I6">
+        <v>3.3333333333333299</v>
+      </c>
+      <c r="J6">
+        <v>2.9777777777777801</v>
+      </c>
+      <c r="K6">
+        <v>6.31111111111111</v>
+      </c>
+      <c r="L6" t="str">
+        <f>IF(G6&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G6&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M6" t="str">
+        <f>IF(K6&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K6&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B7">
-        <v>114.62000684900001</v>
+        <v>122.665972260999</v>
       </c>
       <c r="C7">
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0.8571428571428571</v>
+        <v>1.4285714285714284</v>
       </c>
       <c r="F7">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="G7">
-        <v>2.2017857142857142</v>
+        <v>1.8946428571428573</v>
       </c>
       <c r="H7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="I7">
+        <v>3.1240259819781699</v>
+      </c>
+      <c r="J7">
+        <v>3.3897326402666099</v>
+      </c>
+      <c r="K7">
+        <v>6.6226642104898596</v>
+      </c>
+      <c r="L7" t="str">
+        <f>IF(G7&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G7&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M7" t="str">
+        <f>IF(K7&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K7&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>4.2164203195200001</v>
+      </c>
+      <c r="C8">
+        <v>1.8</v>
+      </c>
+      <c r="D8">
+        <v>1.5</v>
+      </c>
+      <c r="E8">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>1.7535714285714286</v>
+      </c>
+      <c r="H8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8">
+        <v>5.2733511728608899</v>
+      </c>
+      <c r="J8">
+        <v>3.4208629776817001</v>
+      </c>
+      <c r="K8">
+        <v>8.6711979037506097</v>
+      </c>
+      <c r="L8" t="str">
+        <f>IF(G8&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G8&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M8" t="str">
+        <f>IF(K8&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K8&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="2">
         <v>195.19672245000001</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="2">
         <v>2</v>
       </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
         <v>1.4285714285714284</v>
       </c>
-      <c r="F8">
+      <c r="F9" s="2">
         <v>2.25</v>
       </c>
-      <c r="G8">
+      <c r="G9" s="2">
         <v>2.1696428571428572</v>
       </c>
-      <c r="H8" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9">
-        <v>43.110311660000001</v>
-      </c>
-      <c r="C9">
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>2.25</v>
-      </c>
-      <c r="G9">
-        <v>2.1625000000000001</v>
-      </c>
-      <c r="H9" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3.5075018687523101</v>
+      </c>
+      <c r="J9" s="2">
+        <v>3.6399000145712601</v>
+      </c>
+      <c r="K9" s="2">
+        <v>7.2092770918856797</v>
+      </c>
+      <c r="L9" s="2" t="str">
+        <f>IF(G9&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G9&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M9" s="2" t="str">
+        <f>IF(K9&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K9&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B10">
-        <v>169.551014127</v>
+        <v>90.816483914100004</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E10">
-        <v>1.1428571428571428</v>
+        <v>1.2857142857142856</v>
       </c>
       <c r="F10">
         <v>2.5</v>
       </c>
       <c r="G10">
-        <v>2.1607142857142856</v>
+        <v>1.8214285714285714</v>
       </c>
       <c r="H10" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="I10">
+        <v>3.8360053804533001</v>
+      </c>
+      <c r="J10">
+        <v>3.7339468026957499</v>
+      </c>
+      <c r="K10">
+        <v>7.61354614287188</v>
+      </c>
+      <c r="L10" t="str">
+        <f>IF(G10&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G10&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M10" t="str">
+        <f>IF(K10&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K10&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B11">
-        <v>97.141262682700003</v>
+        <v>114.62000684900001</v>
       </c>
       <c r="C11">
-        <v>2.8000000000000003</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D11">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>1.2857142857142856</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F11">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="G11">
-        <v>2.0839285714285714</v>
+        <v>2.2017857142857142</v>
       </c>
       <c r="H11" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="I11">
+        <v>4.4517730934267199</v>
+      </c>
+      <c r="J11">
+        <v>3.7645070714748599</v>
+      </c>
+      <c r="K11">
+        <v>8.2690787067913103</v>
+      </c>
+      <c r="L11" t="str">
+        <f>IF(G11&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G11&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF(K11&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K11&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B12">
-        <v>182.860403915999</v>
+        <v>18.352812943499899</v>
       </c>
       <c r="C12">
-        <v>1.4000000000000001</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="D12">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>1.5714285714285714</v>
       </c>
       <c r="F12">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="G12">
-        <v>2.0553571428571429</v>
+        <v>1.6303571428571428</v>
       </c>
       <c r="H12" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="I12">
+        <v>4.8327449501888298</v>
+      </c>
+      <c r="J12">
+        <v>3.77261957037928</v>
+      </c>
+      <c r="K12">
+        <v>8.7328848321828598</v>
+      </c>
+      <c r="L12" t="str">
+        <f>IF(G12&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G12&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M12" t="str">
+        <f>IF(K12&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K12&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B13">
-        <v>24.2876317204</v>
+        <v>20.004861967899899</v>
       </c>
       <c r="C13">
-        <v>2.2000000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>1.5714285714285714</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13">
-        <v>2.0499999999999998</v>
+        <v>1.7428571428571429</v>
       </c>
       <c r="H13" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I13">
+        <v>4.5423863061659997</v>
+      </c>
+      <c r="J13">
+        <v>3.81766399640127</v>
+      </c>
+      <c r="K13">
+        <v>8.3156069804714807</v>
+      </c>
+      <c r="L13" t="str">
+        <f>IF(G13&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G13&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M13" t="str">
+        <f>IF(K13&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K13&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B14">
-        <v>96.577199252</v>
+        <v>35.996736132800002</v>
       </c>
       <c r="C14">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="D14">
+        <v>2.5</v>
+      </c>
+      <c r="E14">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F14">
+        <v>1.75</v>
+      </c>
+      <c r="G14">
+        <v>1.8696428571428569</v>
+      </c>
+      <c r="H14" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14">
+        <v>3.52597150391097</v>
+      </c>
+      <c r="J14">
+        <v>3.9362873822781399</v>
+      </c>
+      <c r="K14">
+        <v>7.5559547708761201</v>
+      </c>
+      <c r="L14" t="str">
+        <f>IF(G14&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G14&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M14" t="str">
+        <f>IF(K14&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K14&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>97.643793810199895</v>
+      </c>
+      <c r="C15">
+        <v>1.8</v>
+      </c>
+      <c r="D15">
+        <v>1.5</v>
+      </c>
+      <c r="E15">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="E14">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="F14">
-        <v>2.5</v>
-      </c>
-      <c r="G14">
-        <v>1.9607142857142859</v>
-      </c>
-      <c r="H14" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15">
-        <v>123.780828525</v>
-      </c>
-      <c r="C15">
-        <v>2.1</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="F15">
-        <v>1.5</v>
-      </c>
       <c r="G15">
-        <v>1.9357142857142855</v>
+        <v>1.7535714285714286</v>
       </c>
       <c r="H15" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I15">
+        <v>4.2912267641406103</v>
+      </c>
+      <c r="J15">
+        <v>3.9593850797263799</v>
+      </c>
+      <c r="K15">
+        <v>8.3797626767806399</v>
+      </c>
+      <c r="L15" t="str">
+        <f>IF(G15&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G15&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M15" t="str">
+        <f>IF(K15&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K15&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="B16">
-        <v>34.463288233299899</v>
+        <v>169.551014127</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>1.1428571428571428</v>
       </c>
       <c r="F16">
+        <v>2.5</v>
+      </c>
+      <c r="G16">
+        <v>2.1607142857142856</v>
+      </c>
+      <c r="H16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16">
+        <v>5.1151189581565104</v>
+      </c>
+      <c r="J16">
+        <v>4.1874377677755197</v>
+      </c>
+      <c r="K16">
+        <v>9.3462807991376504</v>
+      </c>
+      <c r="L16" t="str">
+        <f>IF(G16&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G16&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M16" t="str">
+        <f>IF(K16&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K16&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2">
+        <v>56.3240863179999</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.8660714285714286</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="2">
+        <v>4.4776605315806703</v>
+      </c>
+      <c r="J17" s="2">
+        <v>4.2522676611259698</v>
+      </c>
+      <c r="K17" s="2">
+        <v>8.8751018466907308</v>
+      </c>
+      <c r="L17" s="2" t="str">
+        <f>IF(G17&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G17&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M17" s="2" t="str">
+        <f>IF(K17&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K17&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="2">
+        <v>34.463288233299899</v>
+      </c>
+      <c r="C18" s="2">
         <v>2</v>
       </c>
-      <c r="G16">
+      <c r="D18" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
         <v>1.9107142857142856</v>
       </c>
-      <c r="H16" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="H18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="2">
+        <v>4.4184725206345004</v>
+      </c>
+      <c r="J18" s="2">
+        <v>4.2802790257878698</v>
+      </c>
+      <c r="K18" s="2">
+        <v>8.6801308633645498</v>
+      </c>
+      <c r="L18" s="2" t="str">
+        <f>IF(G18&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G18&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M18" s="2" t="str">
+        <f>IF(K18&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K18&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="2">
+        <v>20.8341330292</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.01669429658706</v>
+      </c>
+      <c r="J19" s="2">
+        <v>4.3051283471743602</v>
+      </c>
+      <c r="K19" s="2">
+        <v>10.310452253802</v>
+      </c>
+      <c r="L19" s="2" t="str">
+        <f>IF(G19&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G19&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M19" s="2" t="str">
+        <f>IF(K19&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K19&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20">
+        <v>76.142924098199899</v>
+      </c>
+      <c r="C20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F20">
+        <v>2.25</v>
+      </c>
+      <c r="G20">
+        <v>1.7303571428571429</v>
+      </c>
+      <c r="H20" t="s">
+        <v>106</v>
+      </c>
+      <c r="I20">
+        <v>3.4992701273120699</v>
+      </c>
+      <c r="J20">
+        <v>4.313728569976</v>
+      </c>
+      <c r="K20">
+        <v>7.8822738777675303</v>
+      </c>
+      <c r="L20" t="str">
+        <f>IF(G20&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G20&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M20" t="str">
+        <f>IF(K20&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K20&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>76</v>
       </c>
-      <c r="B17">
+      <c r="B21">
         <v>168.085317269</v>
       </c>
-      <c r="C17">
+      <c r="C21">
         <v>2.3000000000000003</v>
       </c>
-      <c r="D17">
+      <c r="D21">
         <v>2</v>
       </c>
-      <c r="E17">
+      <c r="E21">
         <v>1.5714285714285714</v>
-      </c>
-      <c r="F17">
-        <v>1.75</v>
-      </c>
-      <c r="G17">
-        <v>1.905357142857143</v>
-      </c>
-      <c r="H17" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18">
-        <v>122.665972260999</v>
-      </c>
-      <c r="C18">
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F18">
-        <v>1.75</v>
-      </c>
-      <c r="G18">
-        <v>1.8946428571428573</v>
-      </c>
-      <c r="H18" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19">
-        <v>16.2004129271</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>2.5</v>
-      </c>
-      <c r="E19">
-        <v>1.2857142857142856</v>
-      </c>
-      <c r="F19">
-        <v>1.75</v>
-      </c>
-      <c r="G19">
-        <v>1.8839285714285714</v>
-      </c>
-      <c r="H19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20">
-        <v>35.996736132800002</v>
-      </c>
-      <c r="C20">
-        <v>1.8</v>
-      </c>
-      <c r="D20">
-        <v>2.5</v>
-      </c>
-      <c r="E20">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F20">
-        <v>1.75</v>
-      </c>
-      <c r="G20">
-        <v>1.8696428571428569</v>
-      </c>
-      <c r="H20" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21">
-        <v>56.3240863179999</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <v>1.7142857142857142</v>
       </c>
       <c r="F21">
         <v>1.75</v>
       </c>
       <c r="G21">
-        <v>1.8660714285714286</v>
+        <v>1.905357142857143</v>
       </c>
       <c r="H21" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="I21">
+        <v>3.9878234673272401</v>
+      </c>
+      <c r="J21">
+        <v>4.3410342148535497</v>
+      </c>
+      <c r="K21">
+        <v>8.4049344413746301</v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(G21&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G21&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(K21&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K21&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N21" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B22">
-        <v>107.274382185999</v>
+        <v>97.141262682700003</v>
       </c>
       <c r="C22">
-        <v>2.1</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D22">
+        <v>2.5</v>
+      </c>
+      <c r="E22">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F22">
+        <v>1.75</v>
+      </c>
+      <c r="G22">
+        <v>2.0839285714285714</v>
+      </c>
+      <c r="H22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22">
+        <v>3.4716351455200098</v>
+      </c>
+      <c r="J22">
+        <v>4.3555306807529304</v>
+      </c>
+      <c r="K22">
+        <v>7.8801904442002098</v>
+      </c>
+      <c r="L22" t="str">
+        <f>IF(G22&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G22&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M22" t="str">
+        <f>IF(K22&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K22&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>76.826502077599898</v>
+      </c>
+      <c r="C23">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="D23">
+        <v>2.5</v>
+      </c>
+      <c r="E23">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F23">
+        <v>1.75</v>
+      </c>
+      <c r="G23">
+        <v>1.7910714285714286</v>
+      </c>
+      <c r="H23" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23">
+        <v>3.1099701395552999</v>
+      </c>
+      <c r="J23">
+        <v>4.3667239926268699</v>
+      </c>
+      <c r="K23">
+        <v>7.5357983957416304</v>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(G23&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G23&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M23" t="str">
+        <f>IF(K23&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K23&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24">
+        <v>44.268066668400003</v>
+      </c>
+      <c r="C24">
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1.3535714285714286</v>
+      </c>
+      <c r="H24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24">
+        <v>3.1641874020646701</v>
+      </c>
+      <c r="J24">
+        <v>4.5020440390842804</v>
+      </c>
+      <c r="K24">
+        <v>7.6005973356547196</v>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(G24&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G24&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M24" t="str">
+        <f>IF(K24&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K24&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25">
+        <v>27.275757023800001</v>
+      </c>
+      <c r="C25">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D25">
         <v>2</v>
       </c>
-      <c r="E22">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="F22">
-        <v>2.5</v>
-      </c>
-      <c r="G22">
-        <v>1.8642857142857141</v>
-      </c>
-      <c r="H22" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23">
-        <v>90.816483914100004</v>
-      </c>
-      <c r="C23">
+      <c r="E25">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F25">
         <v>2</v>
       </c>
-      <c r="D23">
-        <v>1.5</v>
-      </c>
-      <c r="E23">
-        <v>1.2857142857142856</v>
-      </c>
-      <c r="F23">
-        <v>2.5</v>
-      </c>
-      <c r="G23">
-        <v>1.8214285714285714</v>
-      </c>
-      <c r="H23" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24">
-        <v>13.9860489811</v>
-      </c>
-      <c r="C24">
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="D24">
+      <c r="G25">
+        <v>1.7428571428571429</v>
+      </c>
+      <c r="H25" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25">
+        <v>4.3628167741649104</v>
+      </c>
+      <c r="J25">
+        <v>4.6113600633839402</v>
+      </c>
+      <c r="K25">
+        <v>9.0771549234860007</v>
+      </c>
+      <c r="L25" t="str">
+        <f>IF(G25&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G25&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M25" t="str">
+        <f>IF(K25&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K25&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26">
+        <v>76.8165697300999</v>
+      </c>
+      <c r="C26">
         <v>2</v>
       </c>
-      <c r="E24">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="F24">
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F26">
+        <v>2.75</v>
+      </c>
+      <c r="G26">
+        <v>1.7946428571428572</v>
+      </c>
+      <c r="H26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26">
+        <v>3.5790416448975799</v>
+      </c>
+      <c r="J26">
+        <v>4.6554437747872397</v>
+      </c>
+      <c r="K26">
+        <v>8.2971016602477796</v>
+      </c>
+      <c r="L26" t="str">
+        <f>IF(G26&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G26&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M26" t="str">
+        <f>IF(K26&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K26&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N26" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27">
+        <v>75.904228896299898</v>
+      </c>
+      <c r="C27">
+        <v>1.6</v>
+      </c>
+      <c r="D27">
         <v>2</v>
       </c>
-      <c r="G24">
-        <v>1.8142857142857143</v>
-      </c>
-      <c r="H24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25">
-        <v>76.8165697300999</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F25">
-        <v>2.75</v>
-      </c>
-      <c r="G25">
-        <v>1.7946428571428572</v>
-      </c>
-      <c r="H25" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26">
-        <v>76.826502077599898</v>
-      </c>
-      <c r="C26">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="D26">
-        <v>2.5</v>
-      </c>
-      <c r="E26">
-        <v>1.7142857142857142</v>
-      </c>
-      <c r="F26">
-        <v>1.75</v>
-      </c>
-      <c r="G26">
-        <v>1.7910714285714286</v>
-      </c>
-      <c r="H26" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27">
-        <v>60.320465667299899</v>
-      </c>
-      <c r="C27">
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="D27">
-        <v>1.5</v>
-      </c>
       <c r="E27">
-        <v>1.5714285714285714</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="F27">
         <v>2.25</v>
       </c>
       <c r="G27">
-        <v>1.7553571428571428</v>
+        <v>1.7482142857142857</v>
       </c>
       <c r="H27" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I27">
+        <v>4.9954319144745201</v>
+      </c>
+      <c r="J27">
+        <v>4.6781994775229503</v>
+      </c>
+      <c r="K27">
+        <v>9.6799581093591005</v>
+      </c>
+      <c r="L27" t="str">
+        <f>IF(G27&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G27&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M27" t="str">
+        <f>IF(K27&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K27&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N27" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B28">
-        <v>97.643793810199895</v>
+        <v>21.4947777289999</v>
       </c>
       <c r="C28">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1.2142857142857144</v>
+      </c>
+      <c r="H28" t="s">
+        <v>106</v>
+      </c>
+      <c r="I28">
+        <v>5.3442637198049701</v>
+      </c>
+      <c r="J28">
+        <v>4.7167966840925297</v>
+      </c>
+      <c r="K28">
+        <v>10.0784444257134</v>
+      </c>
+      <c r="L28" t="str">
+        <f>IF(G28&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G28&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M28" t="str">
+        <f>IF(K28&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K28&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29">
+        <v>21.489188390100001</v>
+      </c>
+      <c r="C29">
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
         <v>1.5</v>
       </c>
-      <c r="E28">
-        <v>1.7142857142857142</v>
-      </c>
-      <c r="F28">
+      <c r="G29">
+        <v>1.55</v>
+      </c>
+      <c r="H29" t="s">
+        <v>118</v>
+      </c>
+      <c r="I29">
+        <v>5.9893102905842799</v>
+      </c>
+      <c r="J29">
+        <v>4.8926650466791104</v>
+      </c>
+      <c r="K29">
+        <v>10.898091052232401</v>
+      </c>
+      <c r="L29" t="str">
+        <f>IF(G29&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G29&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M29" t="str">
+        <f>IF(K29&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K29&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N29" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="2">
+        <v>16.3123234551</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D30" s="2">
         <v>2</v>
       </c>
-      <c r="G28">
-        <v>1.7535714285714286</v>
-      </c>
-      <c r="H28" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29">
-        <v>4.2164203195200001</v>
-      </c>
-      <c r="C29">
-        <v>1.8</v>
-      </c>
-      <c r="D29">
+      <c r="E30" s="2">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1.7339285714285715</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5.8138288344534699</v>
+      </c>
+      <c r="J30" s="2">
+        <v>4.9050698182603396</v>
+      </c>
+      <c r="K30" s="2">
+        <v>10.6506449485967</v>
+      </c>
+      <c r="L30" s="2" t="str">
+        <f>IF(G30&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G30&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M30" s="2" t="str">
+        <f>IF(K30&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K30&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31">
+        <v>60.320465667299899</v>
+      </c>
+      <c r="C31">
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="D31">
         <v>1.5</v>
-      </c>
-      <c r="E29">
-        <v>1.7142857142857142</v>
-      </c>
-      <c r="F29">
-        <v>2</v>
-      </c>
-      <c r="G29">
-        <v>1.7535714285714286</v>
-      </c>
-      <c r="H29" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30">
-        <v>75.904228896299898</v>
-      </c>
-      <c r="C30">
-        <v>1.6</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="F30">
-        <v>2.25</v>
-      </c>
-      <c r="G30">
-        <v>1.7482142857142857</v>
-      </c>
-      <c r="H30" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31">
-        <v>27.275757023800001</v>
-      </c>
-      <c r="C31">
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
       </c>
       <c r="E31">
         <v>1.5714285714285714</v>
       </c>
       <c r="F31">
+        <v>2.25</v>
+      </c>
+      <c r="G31">
+        <v>1.7553571428571428</v>
+      </c>
+      <c r="H31" t="s">
+        <v>106</v>
+      </c>
+      <c r="I31">
+        <v>3.2998169752365798</v>
+      </c>
+      <c r="J31">
+        <v>4.9933084522401403</v>
+      </c>
+      <c r="K31">
+        <v>8.3694733655690907</v>
+      </c>
+      <c r="L31" t="str">
+        <f>IF(G31&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G31&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF(K31&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K31&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N31" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>41.656805026699899</v>
+      </c>
+      <c r="C32">
         <v>2</v>
       </c>
-      <c r="G31">
-        <v>1.7428571428571429</v>
-      </c>
-      <c r="H31" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32">
-        <v>20.004861967899899</v>
-      </c>
-      <c r="C32">
-        <v>1.4000000000000001</v>
-      </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <v>1.5714285714285714</v>
       </c>
       <c r="F32">
+        <v>1.5</v>
+      </c>
+      <c r="G32">
+        <v>1.5178571428571428</v>
+      </c>
+      <c r="H32" t="s">
+        <v>118</v>
+      </c>
+      <c r="I32">
+        <v>3.8570580346666201</v>
+      </c>
+      <c r="J32">
+        <v>5.0141737083992997</v>
+      </c>
+      <c r="K32">
+        <v>9.0954702664536793</v>
+      </c>
+      <c r="L32" t="str">
+        <f>IF(G32&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G32&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M32" t="str">
+        <f>IF(K32&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K32&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33">
+        <v>16.2004129271</v>
+      </c>
+      <c r="C33">
         <v>2</v>
       </c>
-      <c r="G32">
-        <v>1.7428571428571429</v>
-      </c>
-      <c r="H32" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33">
-        <v>16.3123234551</v>
-      </c>
-      <c r="C33">
-        <v>1.4000000000000001</v>
-      </c>
       <c r="D33">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E33">
         <v>1.2857142857142856</v>
       </c>
       <c r="F33">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="G33">
-        <v>1.7339285714285715</v>
+        <v>1.8839285714285714</v>
       </c>
       <c r="H33" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34">
-        <v>76.142924098199899</v>
-      </c>
-      <c r="C34">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D34">
+        <v>106</v>
+      </c>
+      <c r="I33">
+        <v>5.8111512537812997</v>
+      </c>
+      <c r="J33">
+        <v>5.0190068010942204</v>
+      </c>
+      <c r="K33">
+        <v>10.7658084437035</v>
+      </c>
+      <c r="L33" t="str">
+        <f>IF(G33&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G33&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M33" t="str">
+        <f>IF(K33&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K33&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="2">
+        <v>44.3952689889</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D34" s="2">
         <v>2</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <v>1.5714285714285714</v>
       </c>
-      <c r="F34">
-        <v>2.25</v>
-      </c>
-      <c r="G34">
-        <v>1.7303571428571429</v>
-      </c>
-      <c r="H34" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F34" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1.6178571428571429</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4.8133791220099003</v>
+      </c>
+      <c r="J34" s="2">
+        <v>5.0388847964731296</v>
+      </c>
+      <c r="K34" s="2">
+        <v>9.8862651030165498</v>
+      </c>
+      <c r="L34" s="2" t="str">
+        <f>IF(G34&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G34&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M34" s="2" t="str">
+        <f>IF(K34&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K34&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B35">
-        <v>20.8341330292</v>
+        <v>41.542048884700002</v>
       </c>
       <c r="C35">
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="D35">
         <v>1.5</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>1.4285714285714284</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35">
-        <v>1.7250000000000001</v>
+        <v>1.6321428571428571</v>
       </c>
       <c r="H35" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="I35">
+        <v>4.96781735327313</v>
+      </c>
+      <c r="J35">
+        <v>5.0505861656492099</v>
+      </c>
+      <c r="K35">
+        <v>9.9996749624145895</v>
+      </c>
+      <c r="L35" t="str">
+        <f>IF(G35&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G35&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M35" t="str">
+        <f>IF(K35&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K35&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N35" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="2">
+        <v>20.2626475462</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1.5732142857142857</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I36" s="2">
+        <v>5.2432890559948797</v>
+      </c>
+      <c r="J36" s="2">
+        <v>5.0525066024341996</v>
+      </c>
+      <c r="K36" s="2">
+        <v>10.3435817856756</v>
+      </c>
+      <c r="L36" s="2" t="str">
+        <f>IF(G36&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G36&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M36" s="2" t="str">
+        <f>IF(K36&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K36&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="2">
+        <v>182.860403915999</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F37" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="G37" s="2">
+        <v>2.0553571428571429</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I37" s="2">
+        <v>4.3186246249061204</v>
+      </c>
+      <c r="J37" s="2">
+        <v>5.0674489181876696</v>
+      </c>
+      <c r="K37" s="2">
+        <v>9.5003937491904598</v>
+      </c>
+      <c r="L37" s="2" t="str">
+        <f>IF(G37&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G37&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M37" s="2" t="str">
+        <f>IF(K37&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K37&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="2">
+        <v>206.581413717</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="G38" s="2">
+        <v>2.2625000000000002</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I38" s="2">
+        <v>5.7460382667797303</v>
+      </c>
+      <c r="J38" s="2">
+        <v>5.0892689453948101</v>
+      </c>
+      <c r="K38" s="2">
+        <v>10.9182996598096</v>
+      </c>
+      <c r="L38" s="2" t="str">
+        <f>IF(G38&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G38&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M38" s="2" t="str">
+        <f>IF(K38&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K38&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39">
+        <v>23.3867259365</v>
+      </c>
+      <c r="C39">
+        <v>1.9000000000000001</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F39">
+        <v>2.25</v>
+      </c>
+      <c r="G39">
+        <v>1.5732142857142857</v>
+      </c>
+      <c r="H39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I39">
+        <v>3.7748137293749799</v>
+      </c>
+      <c r="J39">
+        <v>5.1181555208758303</v>
+      </c>
+      <c r="K39">
+        <v>8.9503948084574407</v>
+      </c>
+      <c r="L39" t="str">
+        <f>IF(G39&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G39&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M39" t="str">
+        <f>IF(K39&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K39&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N39" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40">
+        <v>19.5548964086999</v>
+      </c>
+      <c r="C40">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="D40">
+        <v>1.5</v>
+      </c>
+      <c r="E40">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F40">
+        <v>1.25</v>
+      </c>
+      <c r="G40">
+        <v>1.6446428571428573</v>
+      </c>
+      <c r="H40" t="s">
+        <v>108</v>
+      </c>
+      <c r="I40">
+        <v>3.01506882733432</v>
+      </c>
+      <c r="J40">
+        <v>5.1435252984854802</v>
+      </c>
+      <c r="K40">
+        <v>8.3583528957249094</v>
+      </c>
+      <c r="L40" t="str">
+        <f>IF(G40&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G40&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M40" t="str">
+        <f>IF(K40&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K40&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41">
+        <v>97.960131788799899</v>
+      </c>
+      <c r="C41">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D41">
+        <v>2.5</v>
+      </c>
+      <c r="E41">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F41">
+        <v>2.75</v>
+      </c>
+      <c r="G41">
+        <v>2.2089285714285714</v>
+      </c>
+      <c r="H41" t="s">
+        <v>118</v>
+      </c>
+      <c r="I41">
+        <v>5.1709078853269697</v>
+      </c>
+      <c r="J41">
+        <v>5.1594692385595202</v>
+      </c>
+      <c r="K41">
+        <v>10.2802206338116</v>
+      </c>
+      <c r="L41" t="str">
+        <f>IF(G41&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G41&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M41" t="str">
+        <f>IF(K41&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K41&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N41" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="2">
+        <v>43.110311660000001</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="D42" s="2">
+        <v>3</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="G42" s="2">
+        <v>2.1625000000000001</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I42" s="2">
+        <v>5.42565452685038</v>
+      </c>
+      <c r="J42" s="2">
+        <v>5.1621233753224303</v>
+      </c>
+      <c r="K42" s="2">
+        <v>10.597119349480099</v>
+      </c>
+      <c r="L42" s="2" t="str">
+        <f>IF(G42&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G42&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M42" s="2" t="str">
+        <f>IF(K42&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K42&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>63</v>
       </c>
-      <c r="B36">
+      <c r="B43">
         <v>56.814608672299897</v>
       </c>
-      <c r="C36">
+      <c r="C43">
         <v>1.4000000000000001</v>
       </c>
-      <c r="D36">
+      <c r="D43">
         <v>2.5</v>
-      </c>
-      <c r="E36">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="F36">
-        <v>1.75</v>
-      </c>
-      <c r="G36">
-        <v>1.6982142857142857</v>
-      </c>
-      <c r="H36" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37">
-        <v>42.901241016900002</v>
-      </c>
-      <c r="C37">
-        <v>1.8</v>
-      </c>
-      <c r="D37">
-        <v>1.5</v>
-      </c>
-      <c r="E37">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37">
-        <v>1.6821428571428569</v>
-      </c>
-      <c r="H37" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38">
-        <v>19.5548964086999</v>
-      </c>
-      <c r="C38">
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="D38">
-        <v>1.5</v>
-      </c>
-      <c r="E38">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F38">
-        <v>1.25</v>
-      </c>
-      <c r="G38">
-        <v>1.6446428571428573</v>
-      </c>
-      <c r="H38" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39">
-        <v>41.542048884700002</v>
-      </c>
-      <c r="C39">
-        <v>1.6</v>
-      </c>
-      <c r="D39">
-        <v>1.5</v>
-      </c>
-      <c r="E39">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F39">
-        <v>2</v>
-      </c>
-      <c r="G39">
-        <v>1.6321428571428571</v>
-      </c>
-      <c r="H39" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40">
-        <v>18.352812943499899</v>
-      </c>
-      <c r="C40">
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="F40">
-        <v>2.25</v>
-      </c>
-      <c r="G40">
-        <v>1.6303571428571428</v>
-      </c>
-      <c r="H40" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41">
-        <v>44.3952689889</v>
-      </c>
-      <c r="C41">
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="D41">
-        <v>2</v>
-      </c>
-      <c r="E41">
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="F41">
-        <v>1.5</v>
-      </c>
-      <c r="G41">
-        <v>1.6178571428571429</v>
-      </c>
-      <c r="H41" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42">
-        <v>20.2626475462</v>
-      </c>
-      <c r="C42">
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="D42">
-        <v>1.5</v>
-      </c>
-      <c r="E42">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="F42">
-        <v>2.25</v>
-      </c>
-      <c r="G42">
-        <v>1.5732142857142857</v>
-      </c>
-      <c r="H42" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43">
-        <v>23.3867259365</v>
-      </c>
-      <c r="C43">
-        <v>1.9000000000000001</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
       </c>
       <c r="E43">
         <v>1.1428571428571428</v>
       </c>
       <c r="F43">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="G43">
-        <v>1.5732142857142857</v>
+        <v>1.6982142857142857</v>
       </c>
       <c r="H43" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44">
-        <v>3.4067871411100001</v>
-      </c>
-      <c r="C44">
-        <v>1.6</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="E44">
+        <v>106</v>
+      </c>
+      <c r="I43">
+        <v>5.3681220920335297</v>
+      </c>
+      <c r="J43">
+        <v>5.20892068047125</v>
+      </c>
+      <c r="K43">
+        <v>10.6509732173021</v>
+      </c>
+      <c r="L43" t="str">
+        <f>IF(G43&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G43&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M43" t="str">
+        <f>IF(K43&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K43&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="2">
+        <v>84.428982097299894</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2">
         <v>1.4285714285714284</v>
       </c>
-      <c r="F44">
-        <v>1.25</v>
-      </c>
-      <c r="G44">
-        <v>1.5696428571428571</v>
-      </c>
-      <c r="H44" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45">
-        <v>21.489188390100001</v>
-      </c>
-      <c r="C45">
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="D45">
-        <v>2</v>
-      </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>1.5</v>
-      </c>
-      <c r="G45">
-        <v>1.55</v>
-      </c>
-      <c r="H45" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F44" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G44" s="2">
+        <v>2.3071428571428574</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I44" s="2">
+        <v>6.0364748156282904</v>
+      </c>
+      <c r="J44" s="2">
+        <v>5.3382526133504102</v>
+      </c>
+      <c r="K44" s="2">
+        <v>11.317135841328</v>
+      </c>
+      <c r="L44" s="2" t="str">
+        <f>IF(G44&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G44&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M44" s="2" t="str">
+        <f>IF(K44&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K44&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="107">
+        <v>190.605222900999</v>
+      </c>
+      <c r="C45" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="G45" s="2">
+        <v>2.3125</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I45" s="2">
+        <v>5.3188844490389604</v>
+      </c>
+      <c r="J45" s="2">
+        <v>5.4729558012533701</v>
+      </c>
+      <c r="K45" s="2">
+        <v>10.879752512584799</v>
+      </c>
+      <c r="L45" s="2" t="str">
+        <f>IF(G45&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G45&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M45" s="2" t="str">
+        <f>IF(K45&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K45&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="B46">
-        <v>6.5691873898299997</v>
+        <v>13.9860489811</v>
       </c>
       <c r="C46">
-        <v>1.2000000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46">
-        <v>1.4285714285714284</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <v>1.8142857142857143</v>
+      </c>
+      <c r="H46" t="s">
+        <v>106</v>
+      </c>
+      <c r="I46">
+        <v>4.25</v>
+      </c>
+      <c r="J46">
+        <v>5.4783036767675402</v>
+      </c>
+      <c r="K46">
+        <v>9.8868419284005</v>
+      </c>
+      <c r="L46" t="str">
+        <f>IF(G46&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G46&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M46" t="str">
+        <f>IF(K46&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K46&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N46" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="2">
+        <v>123.780828525</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F47" s="2">
         <v>1.5</v>
       </c>
-      <c r="G46">
-        <v>1.532142857142857</v>
-      </c>
-      <c r="H46" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47">
-        <v>42.291837041199898</v>
-      </c>
-      <c r="C47">
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47">
-        <v>1.7142857142857142</v>
-      </c>
-      <c r="F47">
-        <v>2</v>
-      </c>
-      <c r="G47">
-        <v>1.5285714285714287</v>
-      </c>
-      <c r="H47" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G47" s="2">
+        <v>1.9357142857142855</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I47" s="2">
+        <v>4.86644547877885</v>
+      </c>
+      <c r="J47" s="2">
+        <v>5.4917535899976802</v>
+      </c>
+      <c r="K47" s="2">
+        <v>10.433474203753301</v>
+      </c>
+      <c r="L47" s="2" t="str">
+        <f>IF(G47&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G47&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M47" s="2" t="str">
+        <f>IF(K47&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K47&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B48">
-        <v>16.0307517201</v>
+        <v>4.1639821022800003</v>
       </c>
       <c r="C48">
-        <v>1.4000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="D48">
         <v>1.5</v>
       </c>
       <c r="E48">
-        <v>1.4285714285714284</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="F48">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="G48">
-        <v>1.5196428571428573</v>
+        <v>1.4107142857142856</v>
       </c>
       <c r="H48" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="I48">
+        <v>3.1681705757502501</v>
+      </c>
+      <c r="J48">
+        <v>5.5897645171161896</v>
+      </c>
+      <c r="K48">
+        <v>8.9806008399560397</v>
+      </c>
+      <c r="L48" t="str">
+        <f>IF(G48&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G48&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M48" t="str">
+        <f>IF(K48&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K48&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="N48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="B49">
-        <v>41.656805026699899</v>
+        <v>107.274382185999</v>
       </c>
       <c r="C49">
+        <v>2.1</v>
+      </c>
+      <c r="D49">
         <v>2</v>
       </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
       <c r="E49">
-        <v>1.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F49">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G49">
-        <v>1.5178571428571428</v>
+        <v>1.8642857142857141</v>
       </c>
       <c r="H49" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I49">
+        <v>5.1937883314835398</v>
+      </c>
+      <c r="J49">
+        <v>5.6008816159877401</v>
+      </c>
+      <c r="K49">
+        <v>10.883453597196301</v>
+      </c>
+      <c r="L49" t="str">
+        <f>IF(G49&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G49&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Medium</v>
+      </c>
+      <c r="M49" t="str">
+        <f>IF(K49&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K49&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N49" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B50">
-        <v>32.8099010761999</v>
+        <v>24.2876317204</v>
       </c>
       <c r="C50">
-        <v>2.3000000000000003</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D50">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>1.1428571428571428</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>1.4857142857142858</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="H50" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I50">
+        <v>5.2718013391626304</v>
+      </c>
+      <c r="J50">
+        <v>5.6026443098301897</v>
+      </c>
+      <c r="K50">
+        <v>10.9189878166705</v>
+      </c>
+      <c r="L50" t="str">
+        <f>IF(G50&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G50&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M50" t="str">
+        <f>IF(K50&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K50&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N50" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B51">
-        <v>26.949391069800001</v>
+        <v>12.0349357255</v>
       </c>
       <c r="C51">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51">
-        <v>1.7142857142857142</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>1.25</v>
       </c>
       <c r="G51">
-        <v>1.4410714285714286</v>
+        <v>1.2124999999999999</v>
       </c>
       <c r="H51" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52">
-        <v>4.1639821022800003</v>
-      </c>
-      <c r="C52">
+        <v>118</v>
+      </c>
+      <c r="I51">
+        <v>5.9575816177873104</v>
+      </c>
+      <c r="J51">
+        <v>5.68870176630573</v>
+      </c>
+      <c r="K51">
+        <v>11.8245569304335</v>
+      </c>
+      <c r="L51" t="str">
+        <f>IF(G51&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G51&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M51" t="str">
+        <f>IF(K51&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K51&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N51" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="2">
+        <v>96.577199252</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F52" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1.9607142857142859</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I52" s="2">
+        <v>5.84254038600477</v>
+      </c>
+      <c r="J52" s="2">
+        <v>6.0750332749748504</v>
+      </c>
+      <c r="K52" s="2">
+        <v>11.895505804586101</v>
+      </c>
+      <c r="L52" s="2" t="str">
+        <f>IF(G52&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G52&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M52" s="2" t="str">
+        <f>IF(K52&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K52&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="2">
+        <v>108.143126791</v>
+      </c>
+      <c r="C53" s="2">
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F53" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G53" s="2">
+        <v>2.2357142857142858</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I53" s="2">
+        <v>5.18181213983563</v>
+      </c>
+      <c r="J53" s="2">
+        <v>6.0785566159836097</v>
+      </c>
+      <c r="K53" s="2">
+        <v>11.291641354368601</v>
+      </c>
+      <c r="L53" s="2" t="str">
+        <f>IF(G53&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G53&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="M53" s="2" t="str">
+        <f>IF(K53&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K53&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="2">
+        <v>32.8099010761999</v>
+      </c>
+      <c r="C54" s="2">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D54" s="2">
         <v>1.5</v>
       </c>
-      <c r="D52">
+      <c r="E54" s="2">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1.4857142857142858</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I54" s="2">
+        <v>5.5299951241732099</v>
+      </c>
+      <c r="J54" s="2">
+        <v>6.5746000271329299</v>
+      </c>
+      <c r="K54" s="2">
+        <v>12.113883564575699</v>
+      </c>
+      <c r="L54" s="2" t="str">
+        <f>IF(G54&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G54&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M54" s="2" t="str">
+        <f>IF(K54&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K54&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>High</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="2">
+        <v>6.5691873898299997</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F55" s="2">
         <v>1.5</v>
       </c>
-      <c r="E52">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="F52">
+      <c r="G55" s="2">
+        <v>1.532142857142857</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I55" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J55" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K55" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L55" s="2" t="str">
+        <f>IF(G55&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G55&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M55" s="2" t="e">
+        <f>IF(K55&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K55&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" s="2">
+        <v>16.0307517201</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D56" s="2">
         <v>1.5</v>
       </c>
-      <c r="G52">
-        <v>1.4107142857142856</v>
-      </c>
-      <c r="H52" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53">
-        <v>44.268066668400003</v>
-      </c>
-      <c r="C53">
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>1.7142857142857142</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53">
-        <v>1.3535714285714286</v>
-      </c>
-      <c r="H53" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54">
-        <v>95.0268986208999</v>
-      </c>
-      <c r="C54">
+      <c r="E56" s="2">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1.5196428571428573</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I56" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J56" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K56" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L56" s="2" t="str">
+        <f>IF(G56&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G56&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M56" s="2" t="e">
+        <f>IF(K56&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K56&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" s="2">
+        <v>12.5623252127999</v>
+      </c>
+      <c r="C57" s="2">
         <v>1.6</v>
       </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2">
         <v>1.4285714285714284</v>
       </c>
-      <c r="F54">
-        <v>1.25</v>
-      </c>
-      <c r="G54">
-        <v>1.3196428571428571</v>
-      </c>
-      <c r="H54" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>28</v>
-      </c>
-      <c r="B55">
-        <v>12.5623252127999</v>
-      </c>
-      <c r="C55">
-        <v>1.6</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55">
+      <c r="F57" s="2">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2">
         <v>1.2571428571428571</v>
       </c>
-      <c r="H55" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56">
-        <v>21.4947777289999</v>
-      </c>
-      <c r="C56">
-        <v>2</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56">
-        <v>1.2142857142857144</v>
-      </c>
-      <c r="H56" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>68</v>
-      </c>
-      <c r="B57">
-        <v>12.0349357255</v>
-      </c>
-      <c r="C57">
-        <v>1.6</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57">
-        <v>1.25</v>
-      </c>
-      <c r="G57">
-        <v>1.2124999999999999</v>
-      </c>
-      <c r="H57" t="s">
-        <v>254</v>
+      <c r="H57" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I57" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J57" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K57" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L57" s="2" t="str">
+        <f>IF(G57&lt;=SCORE_METHOD!$B$116,"Low",IF(data_MAPPING!G57&lt;=SCORE_METHOD!$C$116,"Medium","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="M57" s="2" t="e">
+        <f>IF(K57&lt;=SCORE_METHOD!$B$112,"Low",IF(data_MAPPING!K57&lt;=SCORE_METHOD!$C$112,"Medium","High"))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H57">
-    <sortCondition descending="1" ref="G2:G57"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K57">
+    <sortCondition ref="J2:J57"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -31888,317 +33480,2781 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252200BE-0053-4974-B4F3-D97846B8FAD7}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77" t="s">
+    <row r="4" spans="1:10" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="69" t="s">
+        <v>297</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="D5" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="E5" s="72" t="s">
         <v>266</v>
       </c>
-      <c r="D3" s="78" t="s">
+      <c r="F5" s="72" t="s">
         <v>267</v>
       </c>
-      <c r="E3" s="78" t="s">
+      <c r="G5" s="72" t="s">
         <v>268</v>
       </c>
-      <c r="F3" s="78" t="s">
+      <c r="H5" s="72" t="s">
         <v>269</v>
       </c>
-      <c r="G3" s="78" t="s">
+      <c r="I5" s="72" t="s">
         <v>270</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="J5" s="73" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="74">
-        <v>190.605222900999</v>
-      </c>
-      <c r="C4" s="75">
+    <row r="6" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="74">
+        <v>5</v>
+      </c>
+      <c r="C6" s="75" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" s="76">
+        <v>98</v>
+      </c>
+      <c r="E6" s="76">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F6" s="80">
         <v>2.5</v>
       </c>
-      <c r="D4" s="75">
-        <v>3</v>
-      </c>
-      <c r="E4" s="75">
-        <v>1</v>
-      </c>
-      <c r="F4" s="75">
+      <c r="G6" s="76">
+        <v>1.29</v>
+      </c>
+      <c r="H6" s="76">
         <v>2.75</v>
       </c>
-      <c r="G4" s="75">
-        <v>2.3125</v>
-      </c>
-      <c r="H4" s="76" t="s">
+      <c r="I6" s="76">
+        <v>2.21</v>
+      </c>
+      <c r="J6" s="75" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="69">
-        <v>84.428982097299894</v>
-      </c>
-      <c r="C5" s="70">
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="D5" s="70">
-        <v>3</v>
-      </c>
-      <c r="E5" s="70">
-        <v>1.4285714285714284</v>
-      </c>
-      <c r="F5" s="70">
-        <v>2.5</v>
-      </c>
-      <c r="G5" s="70">
-        <v>2.3071428571428574</v>
-      </c>
-      <c r="H5" s="61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="69">
-        <v>206.581413717</v>
-      </c>
-      <c r="C6" s="70">
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="D6" s="70">
-        <v>3</v>
-      </c>
-      <c r="E6" s="70">
-        <v>1</v>
-      </c>
-      <c r="F6" s="70">
-        <v>2.75</v>
-      </c>
-      <c r="G6" s="70">
-        <v>2.2625000000000002</v>
-      </c>
-      <c r="H6" s="61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="69">
+      <c r="B7" s="74">
+        <v>1</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>291</v>
+      </c>
+      <c r="D7" s="76">
+        <v>191</v>
+      </c>
+      <c r="E7" s="76">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="80">
+        <v>3</v>
+      </c>
+      <c r="G7" s="76">
+        <v>1</v>
+      </c>
+      <c r="H7" s="76">
+        <v>2.75</v>
+      </c>
+      <c r="I7" s="76">
+        <v>2.31</v>
+      </c>
+      <c r="J7" s="75" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="74">
+        <v>3</v>
+      </c>
+      <c r="C8" s="75" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="76">
+        <v>207</v>
+      </c>
+      <c r="E8" s="76">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F8" s="80">
+        <v>3</v>
+      </c>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
+      <c r="H8" s="76">
+        <v>2.75</v>
+      </c>
+      <c r="I8" s="76">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J8" s="75" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="77">
+        <v>6</v>
+      </c>
+      <c r="C9" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" s="79">
+        <v>115</v>
+      </c>
+      <c r="E9" s="79">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F9" s="81">
+        <v>3</v>
+      </c>
+      <c r="G9" s="79">
+        <v>0.86</v>
+      </c>
+      <c r="H9" s="79">
+        <v>2.75</v>
+      </c>
+      <c r="I9" s="79">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J9" s="78" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="77">
+        <v>2</v>
+      </c>
+      <c r="C10" s="78" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="79">
+        <v>84</v>
+      </c>
+      <c r="E10" s="79">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F10" s="81">
+        <v>3</v>
+      </c>
+      <c r="G10" s="79">
+        <v>1.43</v>
+      </c>
+      <c r="H10" s="79">
+        <v>2.5</v>
+      </c>
+      <c r="I10" s="79">
+        <v>2.31</v>
+      </c>
+      <c r="J10" s="78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="74">
+        <v>9</v>
+      </c>
+      <c r="C11" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="76">
+        <v>170</v>
+      </c>
+      <c r="E11" s="76">
+        <v>2</v>
+      </c>
+      <c r="F11" s="80">
+        <v>3</v>
+      </c>
+      <c r="G11" s="76">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H11" s="76">
+        <v>2.5</v>
+      </c>
+      <c r="I11" s="76">
+        <v>2.16</v>
+      </c>
+      <c r="J11" s="75" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="60" t="s">
+        <v>265</v>
+      </c>
+      <c r="B12" s="77">
+        <v>4</v>
+      </c>
+      <c r="C12" s="78" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" s="79">
+        <v>108</v>
+      </c>
+      <c r="E12" s="79">
+        <v>2.8</v>
+      </c>
+      <c r="F12" s="81">
+        <v>2.5</v>
+      </c>
+      <c r="G12" s="79">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H12" s="79">
+        <v>2.5</v>
+      </c>
+      <c r="I12" s="79">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J12" s="78" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="60" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="74">
+        <v>7</v>
+      </c>
+      <c r="C13" s="75" t="s">
+        <v>295</v>
+      </c>
+      <c r="D13" s="76">
+        <v>195</v>
+      </c>
+      <c r="E13" s="76">
+        <v>2</v>
+      </c>
+      <c r="F13" s="80">
+        <v>3</v>
+      </c>
+      <c r="G13" s="76">
+        <v>1.43</v>
+      </c>
+      <c r="H13" s="76">
+        <v>2.25</v>
+      </c>
+      <c r="I13" s="76">
+        <v>2.17</v>
+      </c>
+      <c r="J13" s="75" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" s="77">
+        <v>8</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>296</v>
+      </c>
+      <c r="D14" s="79">
+        <v>43</v>
+      </c>
+      <c r="E14" s="79">
+        <v>2.4</v>
+      </c>
+      <c r="F14" s="81">
+        <v>3</v>
+      </c>
+      <c r="G14" s="79">
+        <v>1</v>
+      </c>
+      <c r="H14" s="79">
+        <v>2.25</v>
+      </c>
+      <c r="I14" s="79">
+        <v>2.16</v>
+      </c>
+      <c r="J14" s="78" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="77">
+        <v>10</v>
+      </c>
+      <c r="C15" s="78" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="79">
+        <v>97</v>
+      </c>
+      <c r="E15" s="79">
+        <v>2.8</v>
+      </c>
+      <c r="F15" s="81">
+        <v>2.5</v>
+      </c>
+      <c r="G15" s="79">
+        <v>1.29</v>
+      </c>
+      <c r="H15" s="79">
+        <v>1.75</v>
+      </c>
+      <c r="I15" s="79">
+        <v>2.08</v>
+      </c>
+      <c r="J15" s="78" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="93"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="109" t="s">
+        <v>310</v>
+      </c>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="112" t="s">
+        <v>311</v>
+      </c>
+      <c r="I21" s="113"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="115" t="s">
+        <v>312</v>
+      </c>
+      <c r="L21" s="115" t="s">
+        <v>313</v>
+      </c>
+      <c r="M21" s="115" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="95" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="96" t="s">
+        <v>308</v>
+      </c>
+      <c r="D22" s="97" t="s">
+        <v>309</v>
+      </c>
+      <c r="E22" s="97" t="s">
+        <v>315</v>
+      </c>
+      <c r="F22" s="97" t="s">
+        <v>316</v>
+      </c>
+      <c r="G22" s="98" t="s">
+        <v>270</v>
+      </c>
+      <c r="H22" s="96" t="s">
+        <v>303</v>
+      </c>
+      <c r="I22" s="97" t="s">
+        <v>302</v>
+      </c>
+      <c r="J22" s="98" t="s">
+        <v>304</v>
+      </c>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="116"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="101">
+        <v>95.0268986208999</v>
+      </c>
+      <c r="C23" s="100">
+        <v>1.6</v>
+      </c>
+      <c r="D23" s="99">
+        <v>1</v>
+      </c>
+      <c r="E23" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F23" s="99">
+        <v>1.25</v>
+      </c>
+      <c r="G23" s="101">
+        <v>1.3196428571428571</v>
+      </c>
+      <c r="H23" s="100">
+        <v>3.1472760283264498</v>
+      </c>
+      <c r="I23" s="99">
+        <v>2.4124289188575898</v>
+      </c>
+      <c r="J23" s="101">
+        <v>5.6481793579727704</v>
+      </c>
+      <c r="K23" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="101">
+        <v>26.949391069800001</v>
+      </c>
+      <c r="C24" s="100">
+        <v>1.8</v>
+      </c>
+      <c r="D24" s="99">
+        <v>1</v>
+      </c>
+      <c r="E24" s="99">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F24" s="99">
+        <v>1.25</v>
+      </c>
+      <c r="G24" s="101">
+        <v>1.4410714285714286</v>
+      </c>
+      <c r="H24" s="100">
+        <v>3.7234378344332399</v>
+      </c>
+      <c r="I24" s="99">
+        <v>2.6507947947551598</v>
+      </c>
+      <c r="J24" s="101">
+        <v>6.2952041319554404</v>
+      </c>
+      <c r="K24" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M24" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="101">
+        <v>42.901241016900002</v>
+      </c>
+      <c r="C25" s="100">
+        <v>1.8</v>
+      </c>
+      <c r="D25" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E25" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F25" s="99">
+        <v>2</v>
+      </c>
+      <c r="G25" s="101">
+        <v>1.6821428571428569</v>
+      </c>
+      <c r="H25" s="100">
+        <v>3.4583333333333299</v>
+      </c>
+      <c r="I25" s="99">
+        <v>2.7111111111111099</v>
+      </c>
+      <c r="J25" s="101">
+        <v>6.06944444444445</v>
+      </c>
+      <c r="K25" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="101">
+        <v>42.291837041199898</v>
+      </c>
+      <c r="C26" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D26" s="99">
+        <v>1</v>
+      </c>
+      <c r="E26" s="99">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F26" s="99">
+        <v>2</v>
+      </c>
+      <c r="G26" s="101">
+        <v>1.5285714285714287</v>
+      </c>
+      <c r="H26" s="100">
+        <v>2.8444312929403499</v>
+      </c>
+      <c r="I26" s="99">
+        <v>2.7461905105387898</v>
+      </c>
+      <c r="J26" s="101">
+        <v>5.6088888742303498</v>
+      </c>
+      <c r="K26" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="101">
+        <v>3.4067871411100001</v>
+      </c>
+      <c r="C27" s="100">
+        <v>1.6</v>
+      </c>
+      <c r="D27" s="99">
+        <v>2</v>
+      </c>
+      <c r="E27" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F27" s="99">
+        <v>1.25</v>
+      </c>
+      <c r="G27" s="101">
+        <v>1.5696428571428571</v>
+      </c>
+      <c r="H27" s="100">
+        <v>3.3333333333333299</v>
+      </c>
+      <c r="I27" s="99">
+        <v>2.9777777777777801</v>
+      </c>
+      <c r="J27" s="101">
+        <v>6.31111111111111</v>
+      </c>
+      <c r="K27" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="101">
+        <v>122.665972260999</v>
+      </c>
+      <c r="C28" s="100">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="D28" s="99">
+        <v>2</v>
+      </c>
+      <c r="E28" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F28" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G28" s="101">
+        <v>1.8946428571428573</v>
+      </c>
+      <c r="H28" s="100">
+        <v>3.1240259819781699</v>
+      </c>
+      <c r="I28" s="99">
+        <v>3.3897326402666099</v>
+      </c>
+      <c r="J28" s="101">
+        <v>6.6226642104898596</v>
+      </c>
+      <c r="K28" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="101">
+        <v>4.2164203195200001</v>
+      </c>
+      <c r="C29" s="100">
+        <v>1.8</v>
+      </c>
+      <c r="D29" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E29" s="99">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F29" s="99">
+        <v>2</v>
+      </c>
+      <c r="G29" s="101">
+        <v>1.7535714285714286</v>
+      </c>
+      <c r="H29" s="100">
+        <v>5.2733511728608899</v>
+      </c>
+      <c r="I29" s="99">
+        <v>3.4208629776817001</v>
+      </c>
+      <c r="J29" s="101">
+        <v>8.6711979037506097</v>
+      </c>
+      <c r="K29" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L29" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="101">
+        <v>195.19672245000001</v>
+      </c>
+      <c r="C30" s="100">
+        <v>2</v>
+      </c>
+      <c r="D30" s="99">
+        <v>3</v>
+      </c>
+      <c r="E30" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F30" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G30" s="101">
+        <v>2.1696428571428572</v>
+      </c>
+      <c r="H30" s="100">
+        <v>3.5075018687523101</v>
+      </c>
+      <c r="I30" s="99">
+        <v>3.6399000145712601</v>
+      </c>
+      <c r="J30" s="101">
+        <v>7.2092770918856797</v>
+      </c>
+      <c r="K30" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="101">
+        <v>90.816483914100004</v>
+      </c>
+      <c r="C31" s="100">
+        <v>2</v>
+      </c>
+      <c r="D31" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E31" s="99">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F31" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="G31" s="101">
+        <v>1.8214285714285714</v>
+      </c>
+      <c r="H31" s="100">
+        <v>3.8360053804533001</v>
+      </c>
+      <c r="I31" s="99">
+        <v>3.7339468026957499</v>
+      </c>
+      <c r="J31" s="101">
+        <v>7.61354614287188</v>
+      </c>
+      <c r="K31" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L31" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M31" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="101">
+        <v>114.62000684900001</v>
+      </c>
+      <c r="C32" s="100">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D32" s="99">
+        <v>3</v>
+      </c>
+      <c r="E32" s="99">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F32" s="99">
+        <v>2.75</v>
+      </c>
+      <c r="G32" s="101">
+        <v>2.2017857142857142</v>
+      </c>
+      <c r="H32" s="100">
+        <v>4.4517730934267199</v>
+      </c>
+      <c r="I32" s="99">
+        <v>3.7645070714748599</v>
+      </c>
+      <c r="J32" s="101">
+        <v>8.2690787067913103</v>
+      </c>
+      <c r="K32" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="101">
+        <v>18.352812943499899</v>
+      </c>
+      <c r="C33" s="100">
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="D33" s="99">
+        <v>1</v>
+      </c>
+      <c r="E33" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F33" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G33" s="101">
+        <v>1.6303571428571428</v>
+      </c>
+      <c r="H33" s="100">
+        <v>4.8327449501888298</v>
+      </c>
+      <c r="I33" s="99">
+        <v>3.77261957037928</v>
+      </c>
+      <c r="J33" s="101">
+        <v>8.7328848321828598</v>
+      </c>
+      <c r="K33" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L33" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="101">
+        <v>20.004861967899899</v>
+      </c>
+      <c r="C34" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D34" s="99">
+        <v>2</v>
+      </c>
+      <c r="E34" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F34" s="99">
+        <v>2</v>
+      </c>
+      <c r="G34" s="101">
+        <v>1.7428571428571429</v>
+      </c>
+      <c r="H34" s="100">
+        <v>4.5423863061659997</v>
+      </c>
+      <c r="I34" s="99">
+        <v>3.81766399640127</v>
+      </c>
+      <c r="J34" s="101">
+        <v>8.3156069804714807</v>
+      </c>
+      <c r="K34" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L34" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M34" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="101">
+        <v>35.996736132800002</v>
+      </c>
+      <c r="C35" s="100">
+        <v>1.8</v>
+      </c>
+      <c r="D35" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E35" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F35" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G35" s="101">
+        <v>1.8696428571428569</v>
+      </c>
+      <c r="H35" s="100">
+        <v>3.52597150391097</v>
+      </c>
+      <c r="I35" s="99">
+        <v>3.9362873822781399</v>
+      </c>
+      <c r="J35" s="101">
+        <v>7.5559547708761201</v>
+      </c>
+      <c r="K35" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="101">
+        <v>97.643793810199895</v>
+      </c>
+      <c r="C36" s="100">
+        <v>1.8</v>
+      </c>
+      <c r="D36" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E36" s="99">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F36" s="99">
+        <v>2</v>
+      </c>
+      <c r="G36" s="101">
+        <v>1.7535714285714286</v>
+      </c>
+      <c r="H36" s="100">
+        <v>4.2912267641406103</v>
+      </c>
+      <c r="I36" s="99">
+        <v>3.9593850797263799</v>
+      </c>
+      <c r="J36" s="101">
+        <v>8.3797626767806399</v>
+      </c>
+      <c r="K36" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L36" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="101">
+        <v>169.551014127</v>
+      </c>
+      <c r="C37" s="100">
+        <v>2</v>
+      </c>
+      <c r="D37" s="99">
+        <v>3</v>
+      </c>
+      <c r="E37" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F37" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="G37" s="101">
+        <v>2.1607142857142856</v>
+      </c>
+      <c r="H37" s="100">
+        <v>5.1151189581565104</v>
+      </c>
+      <c r="I37" s="99">
+        <v>4.1874377677755197</v>
+      </c>
+      <c r="J37" s="101">
+        <v>9.3462807991376504</v>
+      </c>
+      <c r="K37" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M37" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="101">
+        <v>56.3240863179999</v>
+      </c>
+      <c r="C38" s="100">
+        <v>1</v>
+      </c>
+      <c r="D38" s="99">
+        <v>3</v>
+      </c>
+      <c r="E38" s="99">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F38" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G38" s="101">
+        <v>1.8660714285714286</v>
+      </c>
+      <c r="H38" s="100">
+        <v>4.4776605315806703</v>
+      </c>
+      <c r="I38" s="99">
+        <v>4.2522676611259698</v>
+      </c>
+      <c r="J38" s="101">
+        <v>8.8751018466907308</v>
+      </c>
+      <c r="K38" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L38" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="101">
+        <v>34.463288233299899</v>
+      </c>
+      <c r="C39" s="100">
+        <v>2</v>
+      </c>
+      <c r="D39" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E39" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F39" s="99">
+        <v>2</v>
+      </c>
+      <c r="G39" s="101">
+        <v>1.9107142857142856</v>
+      </c>
+      <c r="H39" s="100">
+        <v>4.4184725206345004</v>
+      </c>
+      <c r="I39" s="99">
+        <v>4.2802790257878698</v>
+      </c>
+      <c r="J39" s="101">
+        <v>8.6801308633645498</v>
+      </c>
+      <c r="K39" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="101">
+        <v>20.8341330292</v>
+      </c>
+      <c r="C40" s="100">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="D40" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E40" s="99">
+        <v>1</v>
+      </c>
+      <c r="F40" s="99">
+        <v>2</v>
+      </c>
+      <c r="G40" s="101">
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="H40" s="100">
+        <v>6.01669429658706</v>
+      </c>
+      <c r="I40" s="99">
+        <v>4.3051283471743602</v>
+      </c>
+      <c r="J40" s="101">
+        <v>10.310452253802</v>
+      </c>
+      <c r="K40" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="101">
+        <v>76.142924098199899</v>
+      </c>
+      <c r="C41" s="100">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D41" s="99">
+        <v>2</v>
+      </c>
+      <c r="E41" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F41" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G41" s="101">
+        <v>1.7303571428571429</v>
+      </c>
+      <c r="H41" s="100">
+        <v>3.4992701273120699</v>
+      </c>
+      <c r="I41" s="99">
+        <v>4.313728569976</v>
+      </c>
+      <c r="J41" s="101">
+        <v>7.8822738777675303</v>
+      </c>
+      <c r="K41" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L41" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M41" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" s="101">
+        <v>168.085317269</v>
+      </c>
+      <c r="C42" s="100">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D42" s="99">
+        <v>2</v>
+      </c>
+      <c r="E42" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F42" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G42" s="101">
+        <v>1.905357142857143</v>
+      </c>
+      <c r="H42" s="100">
+        <v>3.9878234673272401</v>
+      </c>
+      <c r="I42" s="99">
+        <v>4.3410342148535497</v>
+      </c>
+      <c r="J42" s="101">
+        <v>8.4049344413746301</v>
+      </c>
+      <c r="K42" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="101">
+        <v>97.141262682700003</v>
+      </c>
+      <c r="C43" s="100">
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="D43" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E43" s="99">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F43" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G43" s="101">
+        <v>2.0839285714285714</v>
+      </c>
+      <c r="H43" s="100">
+        <v>3.4716351455200098</v>
+      </c>
+      <c r="I43" s="99">
+        <v>4.3555306807529304</v>
+      </c>
+      <c r="J43" s="101">
+        <v>7.8801904442002098</v>
+      </c>
+      <c r="K43" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="101">
+        <v>76.826502077599898</v>
+      </c>
+      <c r="C44" s="100">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="D44" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E44" s="99">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F44" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G44" s="101">
+        <v>1.7910714285714286</v>
+      </c>
+      <c r="H44" s="100">
+        <v>3.1099701395552999</v>
+      </c>
+      <c r="I44" s="99">
+        <v>4.3667239926268699</v>
+      </c>
+      <c r="J44" s="101">
+        <v>7.5357983957416304</v>
+      </c>
+      <c r="K44" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L44" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="101">
+        <v>44.268066668400003</v>
+      </c>
+      <c r="C45" s="100">
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="D45" s="99">
+        <v>1</v>
+      </c>
+      <c r="E45" s="99">
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="F45" s="99">
+        <v>1</v>
+      </c>
+      <c r="G45" s="101">
+        <v>1.3535714285714286</v>
+      </c>
+      <c r="H45" s="100">
+        <v>3.1641874020646701</v>
+      </c>
+      <c r="I45" s="99">
+        <v>4.5020440390842804</v>
+      </c>
+      <c r="J45" s="101">
+        <v>7.6005973356547196</v>
+      </c>
+      <c r="K45" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M45" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="101">
+        <v>27.275757023800001</v>
+      </c>
+      <c r="C46" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D46" s="99">
+        <v>2</v>
+      </c>
+      <c r="E46" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F46" s="99">
+        <v>2</v>
+      </c>
+      <c r="G46" s="101">
+        <v>1.7428571428571429</v>
+      </c>
+      <c r="H46" s="100">
+        <v>4.3628167741649104</v>
+      </c>
+      <c r="I46" s="99">
+        <v>4.6113600633839402</v>
+      </c>
+      <c r="J46" s="101">
+        <v>9.0771549234860007</v>
+      </c>
+      <c r="K46" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L46" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M46" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="101">
+        <v>76.8165697300999</v>
+      </c>
+      <c r="C47" s="100">
+        <v>2</v>
+      </c>
+      <c r="D47" s="99">
+        <v>1</v>
+      </c>
+      <c r="E47" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F47" s="99">
+        <v>2.75</v>
+      </c>
+      <c r="G47" s="101">
+        <v>1.7946428571428572</v>
+      </c>
+      <c r="H47" s="100">
+        <v>3.5790416448975799</v>
+      </c>
+      <c r="I47" s="99">
+        <v>4.6554437747872397</v>
+      </c>
+      <c r="J47" s="101">
+        <v>8.2971016602477796</v>
+      </c>
+      <c r="K47" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L47" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M47" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="101">
+        <v>75.904228896299898</v>
+      </c>
+      <c r="C48" s="100">
+        <v>1.6</v>
+      </c>
+      <c r="D48" s="99">
+        <v>2</v>
+      </c>
+      <c r="E48" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F48" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G48" s="101">
+        <v>1.7482142857142857</v>
+      </c>
+      <c r="H48" s="100">
+        <v>4.9954319144745201</v>
+      </c>
+      <c r="I48" s="99">
+        <v>4.6781994775229503</v>
+      </c>
+      <c r="J48" s="101">
+        <v>9.6799581093591005</v>
+      </c>
+      <c r="K48" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L48" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M48" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="101">
+        <v>21.4947777289999</v>
+      </c>
+      <c r="C49" s="100">
+        <v>2</v>
+      </c>
+      <c r="D49" s="99">
+        <v>1</v>
+      </c>
+      <c r="E49" s="99">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F49" s="99">
+        <v>1</v>
+      </c>
+      <c r="G49" s="101">
+        <v>1.2142857142857144</v>
+      </c>
+      <c r="H49" s="100">
+        <v>5.3442637198049701</v>
+      </c>
+      <c r="I49" s="99">
+        <v>4.7167966840925297</v>
+      </c>
+      <c r="J49" s="101">
+        <v>10.0784444257134</v>
+      </c>
+      <c r="K49" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L49" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M49" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="101">
+        <v>21.489188390100001</v>
+      </c>
+      <c r="C50" s="100">
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="D50" s="99">
+        <v>2</v>
+      </c>
+      <c r="E50" s="99">
+        <v>1</v>
+      </c>
+      <c r="F50" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="G50" s="101">
+        <v>1.55</v>
+      </c>
+      <c r="H50" s="100">
+        <v>5.9893102905842799</v>
+      </c>
+      <c r="I50" s="99">
+        <v>4.8926650466791104</v>
+      </c>
+      <c r="J50" s="101">
+        <v>10.898091052232401</v>
+      </c>
+      <c r="K50" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M50" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="101">
+        <v>16.3123234551</v>
+      </c>
+      <c r="C51" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D51" s="99">
+        <v>2</v>
+      </c>
+      <c r="E51" s="99">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F51" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G51" s="101">
+        <v>1.7339285714285715</v>
+      </c>
+      <c r="H51" s="100">
+        <v>5.8138288344534699</v>
+      </c>
+      <c r="I51" s="99">
+        <v>4.9050698182603396</v>
+      </c>
+      <c r="J51" s="101">
+        <v>10.6506449485967</v>
+      </c>
+      <c r="K51" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L51" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M51" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="101">
+        <v>60.320465667299899</v>
+      </c>
+      <c r="C52" s="100">
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="D52" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E52" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F52" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G52" s="101">
+        <v>1.7553571428571428</v>
+      </c>
+      <c r="H52" s="100">
+        <v>3.2998169752365798</v>
+      </c>
+      <c r="I52" s="99">
+        <v>4.9933084522401403</v>
+      </c>
+      <c r="J52" s="101">
+        <v>8.3694733655690907</v>
+      </c>
+      <c r="K52" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L52" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M52" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="101">
+        <v>41.656805026699899</v>
+      </c>
+      <c r="C53" s="100">
+        <v>2</v>
+      </c>
+      <c r="D53" s="99">
+        <v>1</v>
+      </c>
+      <c r="E53" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F53" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="G53" s="101">
+        <v>1.5178571428571428</v>
+      </c>
+      <c r="H53" s="100">
+        <v>3.8570580346666201</v>
+      </c>
+      <c r="I53" s="99">
+        <v>5.0141737083992997</v>
+      </c>
+      <c r="J53" s="101">
+        <v>9.0954702664536793</v>
+      </c>
+      <c r="K53" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L53" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M53" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="101">
+        <v>16.2004129271</v>
+      </c>
+      <c r="C54" s="100">
+        <v>2</v>
+      </c>
+      <c r="D54" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E54" s="99">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F54" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G54" s="101">
+        <v>1.8839285714285714</v>
+      </c>
+      <c r="H54" s="100">
+        <v>5.8111512537812997</v>
+      </c>
+      <c r="I54" s="99">
+        <v>5.0190068010942204</v>
+      </c>
+      <c r="J54" s="101">
+        <v>10.7658084437035</v>
+      </c>
+      <c r="K54" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L54" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M54" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="101">
+        <v>44.3952689889</v>
+      </c>
+      <c r="C55" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D55" s="99">
+        <v>2</v>
+      </c>
+      <c r="E55" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F55" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="G55" s="101">
+        <v>1.6178571428571429</v>
+      </c>
+      <c r="H55" s="100">
+        <v>4.8133791220099003</v>
+      </c>
+      <c r="I55" s="99">
+        <v>5.0388847964731296</v>
+      </c>
+      <c r="J55" s="101">
+        <v>9.8862651030165498</v>
+      </c>
+      <c r="K55" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L55" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M55" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="101">
+        <v>41.542048884700002</v>
+      </c>
+      <c r="C56" s="100">
+        <v>1.6</v>
+      </c>
+      <c r="D56" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E56" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F56" s="99">
+        <v>2</v>
+      </c>
+      <c r="G56" s="101">
+        <v>1.6321428571428571</v>
+      </c>
+      <c r="H56" s="100">
+        <v>4.96781735327313</v>
+      </c>
+      <c r="I56" s="99">
+        <v>5.0505861656492099</v>
+      </c>
+      <c r="J56" s="101">
+        <v>9.9996749624145895</v>
+      </c>
+      <c r="K56" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M56" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="101">
+        <v>20.2626475462</v>
+      </c>
+      <c r="C57" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D57" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E57" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F57" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G57" s="101">
+        <v>1.5732142857142857</v>
+      </c>
+      <c r="H57" s="100">
+        <v>5.2432890559948797</v>
+      </c>
+      <c r="I57" s="99">
+        <v>5.0525066024341996</v>
+      </c>
+      <c r="J57" s="101">
+        <v>10.3435817856756</v>
+      </c>
+      <c r="K57" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L57" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="101">
+        <v>182.860403915999</v>
+      </c>
+      <c r="C58" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D58" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E58" s="99">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="F58" s="99">
+        <v>2.75</v>
+      </c>
+      <c r="G58" s="101">
+        <v>2.0553571428571429</v>
+      </c>
+      <c r="H58" s="100">
+        <v>4.3186246249061204</v>
+      </c>
+      <c r="I58" s="99">
+        <v>5.0674489181876696</v>
+      </c>
+      <c r="J58" s="101">
+        <v>9.5003937491904598</v>
+      </c>
+      <c r="K58" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L58" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M58" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="60" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="101">
+        <v>206.581413717</v>
+      </c>
+      <c r="C59" s="100">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D59" s="99">
+        <v>3</v>
+      </c>
+      <c r="E59" s="99">
+        <v>1</v>
+      </c>
+      <c r="F59" s="99">
+        <v>2.75</v>
+      </c>
+      <c r="G59" s="101">
+        <v>2.2625000000000002</v>
+      </c>
+      <c r="H59" s="100">
+        <v>5.7460382667797303</v>
+      </c>
+      <c r="I59" s="99">
+        <v>5.0892689453948101</v>
+      </c>
+      <c r="J59" s="101">
+        <v>10.9182996598096</v>
+      </c>
+      <c r="K59" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M59" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="101">
+        <v>23.3867259365</v>
+      </c>
+      <c r="C60" s="100">
+        <v>1.9000000000000001</v>
+      </c>
+      <c r="D60" s="99">
+        <v>1</v>
+      </c>
+      <c r="E60" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F60" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G60" s="101">
+        <v>1.5732142857142857</v>
+      </c>
+      <c r="H60" s="100">
+        <v>3.7748137293749799</v>
+      </c>
+      <c r="I60" s="99">
+        <v>5.1181555208758303</v>
+      </c>
+      <c r="J60" s="101">
+        <v>8.9503948084574407</v>
+      </c>
+      <c r="K60" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L60" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M60" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="101">
+        <v>19.5548964086999</v>
+      </c>
+      <c r="C61" s="100">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="D61" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E61" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F61" s="99">
+        <v>1.25</v>
+      </c>
+      <c r="G61" s="101">
+        <v>1.6446428571428573</v>
+      </c>
+      <c r="H61" s="100">
+        <v>3.01506882733432</v>
+      </c>
+      <c r="I61" s="99">
+        <v>5.1435252984854802</v>
+      </c>
+      <c r="J61" s="101">
+        <v>8.3583528957249094</v>
+      </c>
+      <c r="K61" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L61" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M61" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" s="101">
+        <v>97.960131788799899</v>
+      </c>
+      <c r="C62" s="100">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D62" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E62" s="99">
+        <v>1.2857142857142856</v>
+      </c>
+      <c r="F62" s="99">
+        <v>2.75</v>
+      </c>
+      <c r="G62" s="101">
+        <v>2.2089285714285714</v>
+      </c>
+      <c r="H62" s="100">
+        <v>5.1709078853269697</v>
+      </c>
+      <c r="I62" s="99">
+        <v>5.1594692385595202</v>
+      </c>
+      <c r="J62" s="101">
+        <v>10.2802206338116</v>
+      </c>
+      <c r="K62" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M62" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="101">
+        <v>43.110311660000001</v>
+      </c>
+      <c r="C63" s="100">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="D63" s="99">
+        <v>3</v>
+      </c>
+      <c r="E63" s="99">
+        <v>1</v>
+      </c>
+      <c r="F63" s="99">
+        <v>2.25</v>
+      </c>
+      <c r="G63" s="101">
+        <v>2.1625000000000001</v>
+      </c>
+      <c r="H63" s="100">
+        <v>5.42565452685038</v>
+      </c>
+      <c r="I63" s="99">
+        <v>5.1621233753224303</v>
+      </c>
+      <c r="J63" s="101">
+        <v>10.597119349480099</v>
+      </c>
+      <c r="K63" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L63" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M63" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="101">
+        <v>56.814608672299897</v>
+      </c>
+      <c r="C64" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D64" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="E64" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F64" s="99">
+        <v>1.75</v>
+      </c>
+      <c r="G64" s="101">
+        <v>1.6982142857142857</v>
+      </c>
+      <c r="H64" s="100">
+        <v>5.3681220920335297</v>
+      </c>
+      <c r="I64" s="99">
+        <v>5.20892068047125</v>
+      </c>
+      <c r="J64" s="101">
+        <v>10.6509732173021</v>
+      </c>
+      <c r="K64" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L64" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M64" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B65" s="101">
+        <v>84.428982097299894</v>
+      </c>
+      <c r="C65" s="100">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="D65" s="99">
+        <v>3</v>
+      </c>
+      <c r="E65" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F65" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="G65" s="101">
+        <v>2.3071428571428574</v>
+      </c>
+      <c r="H65" s="100">
+        <v>6.0364748156282904</v>
+      </c>
+      <c r="I65" s="99">
+        <v>5.3382526133504102</v>
+      </c>
+      <c r="J65" s="101">
+        <v>11.317135841328</v>
+      </c>
+      <c r="K65" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L65" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M65" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="101">
+        <v>190.605222900999</v>
+      </c>
+      <c r="C66" s="100">
+        <v>2.5</v>
+      </c>
+      <c r="D66" s="99">
+        <v>3</v>
+      </c>
+      <c r="E66" s="99">
+        <v>1</v>
+      </c>
+      <c r="F66" s="99">
+        <v>2.75</v>
+      </c>
+      <c r="G66" s="101">
+        <v>2.3125</v>
+      </c>
+      <c r="H66" s="100">
+        <v>5.3188844490389604</v>
+      </c>
+      <c r="I66" s="99">
+        <v>5.4729558012533701</v>
+      </c>
+      <c r="J66" s="101">
+        <v>10.879752512584799</v>
+      </c>
+      <c r="K66" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L66" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M66" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="101">
+        <v>13.9860489811</v>
+      </c>
+      <c r="C67" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D67" s="99">
+        <v>2</v>
+      </c>
+      <c r="E67" s="99">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="F67" s="99">
+        <v>2</v>
+      </c>
+      <c r="G67" s="101">
+        <v>1.8142857142857143</v>
+      </c>
+      <c r="H67" s="100">
+        <v>4.25</v>
+      </c>
+      <c r="I67" s="99">
+        <v>5.4783036767675402</v>
+      </c>
+      <c r="J67" s="101">
+        <v>9.8868419284005</v>
+      </c>
+      <c r="K67" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L67" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M67" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="60" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68" s="101">
+        <v>123.780828525</v>
+      </c>
+      <c r="C68" s="100">
+        <v>2.1</v>
+      </c>
+      <c r="D68" s="99">
+        <v>3</v>
+      </c>
+      <c r="E68" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F68" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="G68" s="101">
+        <v>1.9357142857142855</v>
+      </c>
+      <c r="H68" s="100">
+        <v>4.86644547877885</v>
+      </c>
+      <c r="I68" s="99">
+        <v>5.4917535899976802</v>
+      </c>
+      <c r="J68" s="101">
+        <v>10.433474203753301</v>
+      </c>
+      <c r="K68" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L68" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M68" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="B69" s="101">
+        <v>4.1639821022800003</v>
+      </c>
+      <c r="C69" s="100">
+        <v>1.5</v>
+      </c>
+      <c r="D69" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E69" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F69" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="G69" s="101">
+        <v>1.4107142857142856</v>
+      </c>
+      <c r="H69" s="100">
+        <v>3.1681705757502501</v>
+      </c>
+      <c r="I69" s="99">
+        <v>5.5897645171161896</v>
+      </c>
+      <c r="J69" s="101">
+        <v>8.9806008399560397</v>
+      </c>
+      <c r="K69" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L69" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="M69" s="105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="101">
+        <v>107.274382185999</v>
+      </c>
+      <c r="C70" s="100">
+        <v>2.1</v>
+      </c>
+      <c r="D70" s="99">
+        <v>2</v>
+      </c>
+      <c r="E70" s="99">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F70" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="G70" s="101">
+        <v>1.8642857142857141</v>
+      </c>
+      <c r="H70" s="100">
+        <v>5.1937883314835398</v>
+      </c>
+      <c r="I70" s="99">
+        <v>5.6008816159877401</v>
+      </c>
+      <c r="J70" s="101">
+        <v>10.883453597196301</v>
+      </c>
+      <c r="K70" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L70" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M70" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="B71" s="101">
+        <v>24.2876317204</v>
+      </c>
+      <c r="C71" s="100">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D71" s="99">
+        <v>3</v>
+      </c>
+      <c r="E71" s="99">
+        <v>1</v>
+      </c>
+      <c r="F71" s="99">
+        <v>2</v>
+      </c>
+      <c r="G71" s="101">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="H71" s="100">
+        <v>5.2718013391626304</v>
+      </c>
+      <c r="I71" s="99">
+        <v>5.6026443098301897</v>
+      </c>
+      <c r="J71" s="101">
+        <v>10.9189878166705</v>
+      </c>
+      <c r="K71" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L71" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M71" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" s="101">
+        <v>12.0349357255</v>
+      </c>
+      <c r="C72" s="100">
+        <v>1.6</v>
+      </c>
+      <c r="D72" s="99">
+        <v>1</v>
+      </c>
+      <c r="E72" s="99">
+        <v>1</v>
+      </c>
+      <c r="F72" s="99">
+        <v>1.25</v>
+      </c>
+      <c r="G72" s="101">
+        <v>1.2124999999999999</v>
+      </c>
+      <c r="H72" s="100">
+        <v>5.9575816177873104</v>
+      </c>
+      <c r="I72" s="99">
+        <v>5.68870176630573</v>
+      </c>
+      <c r="J72" s="101">
+        <v>11.8245569304335</v>
+      </c>
+      <c r="K72" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L72" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M72" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="101">
+        <v>96.577199252</v>
+      </c>
+      <c r="C73" s="100">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D73" s="99">
+        <v>2</v>
+      </c>
+      <c r="E73" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F73" s="99">
+        <v>2.5</v>
+      </c>
+      <c r="G73" s="101">
+        <v>1.9607142857142859</v>
+      </c>
+      <c r="H73" s="100">
+        <v>5.84254038600477</v>
+      </c>
+      <c r="I73" s="99">
+        <v>6.0750332749748504</v>
+      </c>
+      <c r="J73" s="101">
+        <v>11.895505804586101</v>
+      </c>
+      <c r="K73" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L73" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M73" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="101">
         <v>108.143126791</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C74" s="100">
         <v>2.8000000000000003</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D74" s="99">
         <v>2.5</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E74" s="99">
         <v>1.1428571428571428</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F74" s="99">
         <v>2.5</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G74" s="101">
         <v>2.2357142857142858</v>
       </c>
-      <c r="H7" s="61" t="s">
+      <c r="H74" s="100">
+        <v>5.18181213983563</v>
+      </c>
+      <c r="I74" s="99">
+        <v>6.0785566159836097</v>
+      </c>
+      <c r="J74" s="101">
+        <v>11.291641354368601</v>
+      </c>
+      <c r="K74" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="L74" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M74" s="105" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="69">
-        <v>97.960131788799899</v>
-      </c>
-      <c r="C8" s="70">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="101">
+        <v>32.8099010761999</v>
+      </c>
+      <c r="C75" s="100">
         <v>2.3000000000000003</v>
       </c>
-      <c r="D8" s="70">
-        <v>2.5</v>
-      </c>
-      <c r="E8" s="70">
-        <v>1.2857142857142856</v>
-      </c>
-      <c r="F8" s="70">
-        <v>2.75</v>
-      </c>
-      <c r="G8" s="70">
-        <v>2.2089285714285714</v>
-      </c>
-      <c r="H8" s="61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="69">
-        <v>114.62000684900001</v>
-      </c>
-      <c r="C9" s="70">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D9" s="70">
-        <v>3</v>
-      </c>
-      <c r="E9" s="70">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="F9" s="70">
-        <v>2.75</v>
-      </c>
-      <c r="G9" s="70">
-        <v>2.2017857142857142</v>
-      </c>
-      <c r="H9" s="61" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="B10" s="69">
-        <v>195.19672245000001</v>
-      </c>
-      <c r="C10" s="70">
+      <c r="D75" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E75" s="99">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="F75" s="99">
+        <v>1</v>
+      </c>
+      <c r="G75" s="101">
+        <v>1.4857142857142858</v>
+      </c>
+      <c r="H75" s="100">
+        <v>5.5299951241732099</v>
+      </c>
+      <c r="I75" s="99">
+        <v>6.5746000271329299</v>
+      </c>
+      <c r="J75" s="101">
+        <v>12.113883564575699</v>
+      </c>
+      <c r="K75" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L75" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="M75" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="101">
+        <v>6.5691873898299997</v>
+      </c>
+      <c r="C76" s="100">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="D76" s="99">
         <v>2</v>
       </c>
-      <c r="D10" s="70">
-        <v>3</v>
-      </c>
-      <c r="E10" s="70">
+      <c r="E76" s="99">
         <v>1.4285714285714284</v>
       </c>
-      <c r="F10" s="70">
-        <v>2.25</v>
-      </c>
-      <c r="G10" s="70">
-        <v>2.1696428571428572</v>
-      </c>
-      <c r="H10" s="61" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="69">
-        <v>43.110311660000001</v>
-      </c>
-      <c r="C11" s="70">
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="D11" s="70">
-        <v>3</v>
-      </c>
-      <c r="E11" s="70">
-        <v>1</v>
-      </c>
-      <c r="F11" s="70">
-        <v>2.25</v>
-      </c>
-      <c r="G11" s="70">
-        <v>2.1625000000000001</v>
-      </c>
-      <c r="H11" s="61" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="69">
-        <v>169.551014127</v>
-      </c>
-      <c r="C12" s="70">
-        <v>2</v>
-      </c>
-      <c r="D12" s="70">
-        <v>3</v>
-      </c>
-      <c r="E12" s="70">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="F12" s="70">
-        <v>2.5</v>
-      </c>
-      <c r="G12" s="70">
-        <v>2.1607142857142856</v>
-      </c>
-      <c r="H12" s="61" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="71">
-        <v>97.141262682700003</v>
-      </c>
-      <c r="C13" s="72">
-        <v>2.8000000000000003</v>
-      </c>
-      <c r="D13" s="72">
-        <v>2.5</v>
-      </c>
-      <c r="E13" s="72">
-        <v>1.2857142857142856</v>
-      </c>
-      <c r="F13" s="72">
+      <c r="F76" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="G76" s="101">
+        <v>1.532142857142857</v>
+      </c>
+      <c r="H76" s="100" t="s">
+        <v>314</v>
+      </c>
+      <c r="I76" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="J76" s="101" t="s">
+        <v>314</v>
+      </c>
+      <c r="K76" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L76" s="105" t="s">
+        <v>314</v>
+      </c>
+      <c r="M76" s="105" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B77" s="101">
+        <v>16.0307517201</v>
+      </c>
+      <c r="C77" s="100">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="D77" s="99">
+        <v>1.5</v>
+      </c>
+      <c r="E77" s="99">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F77" s="99">
         <v>1.75</v>
       </c>
-      <c r="G13" s="72">
-        <v>2.0839285714285714</v>
-      </c>
-      <c r="H13" s="64" t="s">
-        <v>108</v>
+      <c r="G77" s="101">
+        <v>1.5196428571428573</v>
+      </c>
+      <c r="H77" s="100" t="s">
+        <v>314</v>
+      </c>
+      <c r="I77" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="101" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L77" s="105" t="s">
+        <v>314</v>
+      </c>
+      <c r="M77" s="105" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B78" s="104">
+        <v>12.5623252127999</v>
+      </c>
+      <c r="C78" s="102">
+        <v>1.6</v>
+      </c>
+      <c r="D78" s="103">
+        <v>1</v>
+      </c>
+      <c r="E78" s="103">
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="F78" s="103">
+        <v>1</v>
+      </c>
+      <c r="G78" s="104">
+        <v>1.2571428571428571</v>
+      </c>
+      <c r="H78" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="I78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="106" t="s">
+        <v>30</v>
+      </c>
+      <c r="L78" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="M78" s="106" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:J15">
+    <sortCondition descending="1" ref="H6:H15"/>
+  </sortState>
+  <mergeCells count="5">
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="M21:M22"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K23:L78">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",K23)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",K23)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",K23)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",K23)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>"if($K$23:$K$78 = ""Low)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K23:K78">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",K23)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10F21B6-AB13-4707-B257-9CFC3BB2FEF5}">
-  <dimension ref="A2:N104"/>
+  <dimension ref="A2:N116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
@@ -32217,22 +36273,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="117" t="s">
         <v>220</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -32700,11 +36756,11 @@
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="1:3" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="85" t="s">
+      <c r="A42" s="120" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="86"/>
-      <c r="C42" s="87"/>
+      <c r="B42" s="121"/>
+      <c r="C42" s="122"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="49" t="s">
@@ -32755,7 +36811,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="80" t="str">
+      <c r="A47" s="70" t="str">
         <v>customer service, stewardship and sustainability, and equity</v>
       </c>
       <c r="B47" s="55">
@@ -32767,17 +36823,17 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="83" t="s">
+      <c r="A50" s="118" t="s">
         <v>239</v>
       </c>
-      <c r="B50" s="83"/>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
+      <c r="B50" s="118"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="118"/>
+      <c r="I50" s="118"/>
     </row>
     <row r="52" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
@@ -32827,10 +36883,10 @@
         <f>VLOOKUP(B53,$A$44:$C$47,3,FALSE)</f>
         <v>0.25</v>
       </c>
-      <c r="G53" s="84" t="s">
+      <c r="G53" s="119" t="s">
         <v>230</v>
       </c>
-      <c r="H53" s="84" t="s">
+      <c r="H53" s="119" t="s">
         <v>233</v>
       </c>
     </row>
@@ -32856,8 +36912,8 @@
         <f t="shared" ref="F54:F75" si="3">VLOOKUP(B54,$A$44:$C$47,3,FALSE)</f>
         <v>0.25</v>
       </c>
-      <c r="G54" s="84"/>
-      <c r="H54" s="84"/>
+      <c r="G54" s="119"/>
+      <c r="H54" s="119"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -32881,8 +36937,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G55" s="84"/>
-      <c r="H55" s="84"/>
+      <c r="G55" s="119"/>
+      <c r="H55" s="119"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -32906,8 +36962,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G56" s="84"/>
-      <c r="H56" s="84"/>
+      <c r="G56" s="119"/>
+      <c r="H56" s="119"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -32931,8 +36987,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G57" s="84"/>
-      <c r="H57" s="84"/>
+      <c r="G57" s="119"/>
+      <c r="H57" s="119"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
@@ -32956,8 +37012,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G58" s="84"/>
-      <c r="H58" s="84"/>
+      <c r="G58" s="119"/>
+      <c r="H58" s="119"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
@@ -32981,8 +37037,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G59" s="84"/>
-      <c r="H59" s="84"/>
+      <c r="G59" s="119"/>
+      <c r="H59" s="119"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
@@ -33006,8 +37062,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G60" s="84"/>
-      <c r="H60" s="84"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="119"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
@@ -33031,8 +37087,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G61" s="84"/>
-      <c r="H61" s="84"/>
+      <c r="G61" s="119"/>
+      <c r="H61" s="119"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -33056,8 +37112,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G62" s="84"/>
-      <c r="H62" s="84"/>
+      <c r="G62" s="119"/>
+      <c r="H62" s="119"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
@@ -33081,8 +37137,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G63" s="84"/>
-      <c r="H63" s="84"/>
+      <c r="G63" s="119"/>
+      <c r="H63" s="119"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
@@ -33106,8 +37162,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G64" s="84"/>
-      <c r="H64" s="84"/>
+      <c r="G64" s="119"/>
+      <c r="H64" s="119"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
@@ -33131,8 +37187,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G65" s="84"/>
-      <c r="H65" s="84"/>
+      <c r="G65" s="119"/>
+      <c r="H65" s="119"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
@@ -33156,8 +37212,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G66" s="84"/>
-      <c r="H66" s="84"/>
+      <c r="G66" s="119"/>
+      <c r="H66" s="119"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -33181,8 +37237,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G67" s="84"/>
-      <c r="H67" s="84"/>
+      <c r="G67" s="119"/>
+      <c r="H67" s="119"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -33206,8 +37262,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G68" s="84"/>
-      <c r="H68" s="84"/>
+      <c r="G68" s="119"/>
+      <c r="H68" s="119"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -33231,8 +37287,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G69" s="84"/>
-      <c r="H69" s="84"/>
+      <c r="G69" s="119"/>
+      <c r="H69" s="119"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -33256,8 +37312,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G70" s="84"/>
-      <c r="H70" s="84"/>
+      <c r="G70" s="119"/>
+      <c r="H70" s="119"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -33281,8 +37337,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G71" s="84"/>
-      <c r="H71" s="84"/>
+      <c r="G71" s="119"/>
+      <c r="H71" s="119"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -33306,8 +37362,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G72" s="84"/>
-      <c r="H72" s="84"/>
+      <c r="G72" s="119"/>
+      <c r="H72" s="119"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -33331,8 +37387,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G73" s="84"/>
-      <c r="H73" s="84"/>
+      <c r="G73" s="119"/>
+      <c r="H73" s="119"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
@@ -33356,8 +37412,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G74" s="84"/>
-      <c r="H74" s="84"/>
+      <c r="G74" s="119"/>
+      <c r="H74" s="119"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -33381,8 +37437,8 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="G75" s="84"/>
-      <c r="H75" s="84"/>
+      <c r="G75" s="119"/>
+      <c r="H75" s="119"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -33863,6 +37919,91 @@
       </c>
       <c r="F104" s="64" t="s">
         <v>247</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="90" t="s">
+        <v>301</v>
+      </c>
+      <c r="B109" s="91">
+        <v>0.33</v>
+      </c>
+      <c r="C109" s="92">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="82" t="s">
+        <v>302</v>
+      </c>
+      <c r="B110" s="16">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!J2:J54,1/3)</f>
+        <v>4.3079950881082398</v>
+      </c>
+      <c r="C110" s="83">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!J2:J54,2/3)</f>
+        <v>5.062468146269846</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="82" t="s">
+        <v>303</v>
+      </c>
+      <c r="B111" s="16">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!I2:I54,1/3)</f>
+        <v>3.8430229318577402</v>
+      </c>
+      <c r="C111" s="83">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!I2:I54,2/3)</f>
+        <v>5.1781773883327435</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="82" t="s">
+        <v>304</v>
+      </c>
+      <c r="B112" s="16">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!K2:K54,1/3)</f>
+        <v>8.3729031359729404</v>
+      </c>
+      <c r="C112" s="83">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!K2:K54,2/3)</f>
+        <v>10.212961897778866</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="82"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="83"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="82"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="83"/>
+    </row>
+    <row r="115" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="B115" s="88">
+        <v>0.33</v>
+      </c>
+      <c r="C115" s="89">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="84" t="s">
+        <v>238</v>
+      </c>
+      <c r="B116" s="85">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!G2:G57,1/3)</f>
+        <v>1.6363095238095238</v>
+      </c>
+      <c r="C116" s="86">
+        <f>_xlfn.PERCENTILE.INC(data_MAPPING!G2:G57,2/3)</f>
+        <v>1.8684523809523808</v>
       </c>
     </row>
   </sheetData>
@@ -36425,45 +40566,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="C1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81" t="s">
+      <c r="C1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81" t="s">
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
       <c r="AA1" t="s">
         <v>92</v>
       </c>
-      <c r="AB1" s="81" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
+      <c r="AB1" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -41334,15 +45475,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="57447674-5de3-4c92-a69b-ff20baefdff4" xsi:nil="true"/>
@@ -41351,6 +45483,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41561,14 +45702,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12B97D2-0A81-4A8F-8993-42BFE2499756}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF9FF8CD-D569-4519-BF10-7CCDCFE5EF79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -41581,6 +45714,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12B97D2-0A81-4A8F-8993-42BFE2499756}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
